--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54061C65-7511-4644-8827-B44D86D6A67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2574" uniqueCount="1006">
   <si>
     <t>Prénom</t>
   </si>
@@ -988,9 +994,6 @@
     <t>Stockholm</t>
   </si>
   <si>
-    <t>Dordrecht</t>
-  </si>
-  <si>
     <t>Dublin</t>
   </si>
   <si>
@@ -1123,9 +1126,6 @@
     <t>Royal Collection</t>
   </si>
   <si>
-    <t>Galleria degli Uffizi</t>
-  </si>
-  <si>
     <t>Cleveland Museum of Art</t>
   </si>
   <si>
@@ -3035,13 +3035,16 @@
   </si>
   <si>
     <t>allemande</t>
+  </si>
+  <si>
+    <t>Pietro di CORTONE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3086,18 +3089,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3135,7 +3146,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3169,6 +3180,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3203,9 +3215,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3378,11 +3391,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X194"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="34.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3456,7 +3472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -3476,31 +3492,31 @@
         <v>294</v>
       </c>
       <c r="J2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="S2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="U2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="W2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -3520,31 +3536,31 @@
         <v>295</v>
       </c>
       <c r="J3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="U3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="W3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -3564,31 +3580,31 @@
         <v>294</v>
       </c>
       <c r="J4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="S4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T4" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="U4" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="W4" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3610,29 +3626,35 @@
       <c r="H5" t="s">
         <v>167</v>
       </c>
+      <c r="I5" t="s">
+        <v>302</v>
+      </c>
+      <c r="J5" t="s">
+        <v>351</v>
+      </c>
       <c r="M5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="S5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="U5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="W5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -3658,34 +3680,34 @@
         <v>296</v>
       </c>
       <c r="J6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="Q6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="S6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="U6" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="W6" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -3711,25 +3733,25 @@
         <v>296</v>
       </c>
       <c r="J7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="S7" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W7" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3755,31 +3777,31 @@
         <v>296</v>
       </c>
       <c r="J8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="S8" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="U8" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="W8" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -3802,37 +3824,40 @@
         <v>296</v>
       </c>
       <c r="J9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="S9" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T9" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="U9" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="W9" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
+      <c r="D10" t="s">
+        <v>1005</v>
+      </c>
       <c r="F10" t="s">
         <v>143</v>
       </c>
@@ -3846,37 +3871,40 @@
         <v>296</v>
       </c>
       <c r="J10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="S10" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T10" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="U10" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="W10" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X10">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
       </c>
+      <c r="D11" t="s">
+        <v>1005</v>
+      </c>
       <c r="F11" t="s">
         <v>143</v>
       </c>
@@ -3890,31 +3918,34 @@
         <v>296</v>
       </c>
       <c r="J11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="S11" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W11" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
+      <c r="D12" t="s">
+        <v>1005</v>
+      </c>
       <c r="F12" t="s">
         <v>143</v>
       </c>
@@ -3928,25 +3959,25 @@
         <v>297</v>
       </c>
       <c r="J12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="S12" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W12" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -3966,31 +3997,31 @@
         <v>298</v>
       </c>
       <c r="J13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M13" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="S13" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T13" t="s">
+        <v>815</v>
+      </c>
+      <c r="U13" t="s">
         <v>817</v>
       </c>
-      <c r="U13" t="s">
-        <v>819</v>
-      </c>
       <c r="W13" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -4010,31 +4041,31 @@
         <v>299</v>
       </c>
       <c r="J14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="S14" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T14" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="U14" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="W14" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4054,31 +4085,31 @@
         <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="S15" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T15" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="U15" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="W15" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X15">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -4098,31 +4129,31 @@
         <v>301</v>
       </c>
       <c r="J16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M16" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="S16" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T16" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="U16" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="W16" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X16">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -4142,31 +4173,31 @@
         <v>302</v>
       </c>
       <c r="J17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="S17" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T17" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="U17" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="W17" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -4186,31 +4217,31 @@
         <v>303</v>
       </c>
       <c r="J18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="S18" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T18" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="U18" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="W18" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X18">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -4230,31 +4261,31 @@
         <v>296</v>
       </c>
       <c r="J19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="S19" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T19" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U19" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="W19" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X19">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -4274,25 +4305,25 @@
         <v>296</v>
       </c>
       <c r="J20" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="S20" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W20" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X20">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -4312,31 +4343,31 @@
         <v>304</v>
       </c>
       <c r="J21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M21" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S21" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T21" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="U21" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="W21" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -4356,31 +4387,31 @@
         <v>296</v>
       </c>
       <c r="J22" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="S22" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T22" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="U22" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="W22" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X22">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -4400,31 +4431,31 @@
         <v>301</v>
       </c>
       <c r="J23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M23" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="S23" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T23" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="U23" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="W23" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -4444,31 +4475,31 @@
         <v>305</v>
       </c>
       <c r="J24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M24" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="S24" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T24" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U24" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="W24" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -4488,31 +4519,31 @@
         <v>306</v>
       </c>
       <c r="J25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="S25" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T25" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="U25" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="W25" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -4532,31 +4563,31 @@
         <v>294</v>
       </c>
       <c r="J26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M26" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="S26" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T26" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="U26" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="W26" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -4576,31 +4607,31 @@
         <v>298</v>
       </c>
       <c r="J27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M27" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="S27" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T27" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="U27" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="W27" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -4620,31 +4651,31 @@
         <v>307</v>
       </c>
       <c r="J28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M28" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="S28" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T28" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U28" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W28" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X28">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -4664,31 +4695,31 @@
         <v>294</v>
       </c>
       <c r="J29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M29" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="S29" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T29" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="U29" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="W29" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X29">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -4708,31 +4739,31 @@
         <v>304</v>
       </c>
       <c r="J30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M30" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="S30" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T30" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="U30" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="W30" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X30">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -4752,31 +4783,31 @@
         <v>301</v>
       </c>
       <c r="J31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M31" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="S31" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T31" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="U31" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="W31" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4796,31 +4827,31 @@
         <v>304</v>
       </c>
       <c r="J32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M32" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S32" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T32" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="U32" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="W32" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -4840,31 +4871,31 @@
         <v>308</v>
       </c>
       <c r="J33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="S33" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T33" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="U33" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="W33" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -4884,31 +4915,31 @@
         <v>301</v>
       </c>
       <c r="J34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="S34" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T34" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="U34" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="W34" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -4928,31 +4959,31 @@
         <v>301</v>
       </c>
       <c r="J35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="S35" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T35" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="U35" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="W35" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X35">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -4972,31 +5003,31 @@
         <v>304</v>
       </c>
       <c r="J36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M36" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="S36" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T36" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="U36" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="W36" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -5016,31 +5047,31 @@
         <v>294</v>
       </c>
       <c r="J37" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="S37" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T37" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="U37" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="W37" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X37">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -5060,31 +5091,31 @@
         <v>309</v>
       </c>
       <c r="J38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="S38" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T38" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="U38" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="W38" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X38">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -5104,31 +5135,31 @@
         <v>301</v>
       </c>
       <c r="J39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="S39" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T39" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="U39" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="W39" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -5148,31 +5179,31 @@
         <v>301</v>
       </c>
       <c r="J40" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="S40" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T40" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="U40" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="W40" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -5192,31 +5223,31 @@
         <v>301</v>
       </c>
       <c r="J41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="S41" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T41" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="U41" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="W41" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X41">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -5236,31 +5267,31 @@
         <v>310</v>
       </c>
       <c r="J42" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="S42" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T42" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="U42" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="W42" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -5280,31 +5311,31 @@
         <v>311</v>
       </c>
       <c r="J43" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M43" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="S43" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T43" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="U43" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="W43" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X43">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -5324,31 +5355,31 @@
         <v>302</v>
       </c>
       <c r="J44" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="S44" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T44" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="U44" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="W44" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X44">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -5368,31 +5399,31 @@
         <v>301</v>
       </c>
       <c r="J45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M45" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="S45" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T45" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="U45" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="W45" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -5412,31 +5443,31 @@
         <v>302</v>
       </c>
       <c r="J46" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M46" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="S46" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T46" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="U46" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="W46" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -5456,31 +5487,31 @@
         <v>302</v>
       </c>
       <c r="J47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M47" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="S47" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T47" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="U47" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="W47" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -5500,31 +5531,31 @@
         <v>304</v>
       </c>
       <c r="J48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M48" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="S48" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T48" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="U48" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="W48" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -5544,31 +5575,31 @@
         <v>302</v>
       </c>
       <c r="J49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="S49" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T49" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="U49" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="W49" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -5588,31 +5619,31 @@
         <v>295</v>
       </c>
       <c r="J50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M50" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="S50" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T50" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="U50" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="W50" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -5632,31 +5663,31 @@
         <v>301</v>
       </c>
       <c r="J51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M51" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="S51" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T51" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="U51" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="W51" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -5676,31 +5707,31 @@
         <v>312</v>
       </c>
       <c r="J52" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M52" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="S52" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T52" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="U52" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="W52" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -5720,31 +5751,31 @@
         <v>294</v>
       </c>
       <c r="J53" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M53" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="S53" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T53" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U53" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W53" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>41</v>
       </c>
@@ -5764,34 +5795,34 @@
         <v>304</v>
       </c>
       <c r="J54" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M54" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Q54" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="S54" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T54" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="U54" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="W54" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>41</v>
       </c>
@@ -5811,31 +5842,31 @@
         <v>295</v>
       </c>
       <c r="J55" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M55" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="S55" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T55" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="U55" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="W55" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -5855,31 +5886,31 @@
         <v>306</v>
       </c>
       <c r="J56" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M56" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="S56" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T56" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U56" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W56" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>41</v>
       </c>
@@ -5899,31 +5930,31 @@
         <v>313</v>
       </c>
       <c r="J57" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M57" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="S57" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T57" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="U57" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="W57" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>42</v>
       </c>
@@ -5949,31 +5980,31 @@
         <v>301</v>
       </c>
       <c r="J58" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M58" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S58" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T58" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="U58" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="W58" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>42</v>
       </c>
@@ -5999,31 +6030,31 @@
         <v>301</v>
       </c>
       <c r="J59" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M59" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="S59" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T59" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="U59" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="W59" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>42</v>
       </c>
@@ -6049,31 +6080,31 @@
         <v>304</v>
       </c>
       <c r="J60" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M60" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="S60" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T60" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="U60" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="W60" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X60">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>42</v>
       </c>
@@ -6099,31 +6130,31 @@
         <v>304</v>
       </c>
       <c r="J61" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M61" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="S61" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T61" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="U61" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="W61" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>43</v>
       </c>
@@ -6143,31 +6174,31 @@
         <v>314</v>
       </c>
       <c r="J62" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M62" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="S62" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T62" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="U62" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="W62" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>43</v>
       </c>
@@ -6187,31 +6218,31 @@
         <v>297</v>
       </c>
       <c r="J63" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M63" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="S63" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T63" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="U63" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="W63" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>43</v>
       </c>
@@ -6231,31 +6262,31 @@
         <v>315</v>
       </c>
       <c r="J64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M64" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="S64" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T64" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="U64" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="W64" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>43</v>
       </c>
@@ -6275,31 +6306,31 @@
         <v>304</v>
       </c>
       <c r="J65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M65" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="S65" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T65" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="U65" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="W65" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X65">
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>44</v>
       </c>
@@ -6319,31 +6350,31 @@
         <v>297</v>
       </c>
       <c r="J66" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="S66" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T66" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="U66" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="W66" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X66">
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>44</v>
       </c>
@@ -6363,31 +6394,31 @@
         <v>316</v>
       </c>
       <c r="J67" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="M67" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="S67" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T67" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="U67" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="W67" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X67">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>44</v>
       </c>
@@ -6407,31 +6438,31 @@
         <v>301</v>
       </c>
       <c r="J68" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M68" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S68" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T68" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="U68" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="W68" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X68">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>45</v>
       </c>
@@ -6451,31 +6482,31 @@
         <v>317</v>
       </c>
       <c r="J69" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M69" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="S69" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T69" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="U69" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="W69" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X69">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>45</v>
       </c>
@@ -6495,25 +6526,25 @@
         <v>297</v>
       </c>
       <c r="J70" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M70" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="S70" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="W70" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>46</v>
       </c>
@@ -6533,31 +6564,31 @@
         <v>294</v>
       </c>
       <c r="J71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M71" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="S71" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T71" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="U71" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="W71" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X71">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>46</v>
       </c>
@@ -6577,34 +6608,34 @@
         <v>304</v>
       </c>
       <c r="J72" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M72" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="Q72" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="S72" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T72" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="U72" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="W72" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -6624,31 +6655,31 @@
         <v>309</v>
       </c>
       <c r="J73" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M73" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="S73" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T73" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="U73" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="W73" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X73">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>46</v>
       </c>
@@ -6668,31 +6699,31 @@
         <v>318</v>
       </c>
       <c r="J74" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M74" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="S74" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T74" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="U74" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="W74" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X74">
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>47</v>
       </c>
@@ -6712,25 +6743,25 @@
         <v>294</v>
       </c>
       <c r="J75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M75" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="S75" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="W75" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X75">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>47</v>
       </c>
@@ -6750,31 +6781,31 @@
         <v>304</v>
       </c>
       <c r="J76" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M76" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="S76" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T76" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="U76" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="W76" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X76">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>48</v>
       </c>
@@ -6794,31 +6825,31 @@
         <v>319</v>
       </c>
       <c r="J77" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M77" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="S77" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T77" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="U77" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="W77" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X77">
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>48</v>
       </c>
@@ -6838,31 +6869,31 @@
         <v>320</v>
       </c>
       <c r="J78" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M78" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S78" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T78" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="U78" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="W78" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X78">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>48</v>
       </c>
@@ -6882,31 +6913,31 @@
         <v>301</v>
       </c>
       <c r="J79" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M79" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="S79" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T79" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="U79" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="W79" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X79">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -6926,31 +6957,31 @@
         <v>304</v>
       </c>
       <c r="J80" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M80" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="S80" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T80" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="U80" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="W80" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X80">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -6970,31 +7001,31 @@
         <v>302</v>
       </c>
       <c r="J81" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M81" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="S81" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T81" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="U81" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="W81" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X81">
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>49</v>
       </c>
@@ -7014,31 +7045,31 @@
         <v>301</v>
       </c>
       <c r="J82" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M82" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="S82" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T82" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="U82" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="W82" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X82">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>49</v>
       </c>
@@ -7058,31 +7089,31 @@
         <v>321</v>
       </c>
       <c r="J83" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M83" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S83" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T83" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="U83" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="W83" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X83">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>49</v>
       </c>
@@ -7102,31 +7133,31 @@
         <v>321</v>
       </c>
       <c r="J84" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M84" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="S84" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T84" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="U84" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="W84" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X84">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>49</v>
       </c>
@@ -7146,25 +7177,25 @@
         <v>321</v>
       </c>
       <c r="J85" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M85" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="S85" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="W85" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>50</v>
       </c>
@@ -7184,31 +7215,31 @@
         <v>301</v>
       </c>
       <c r="J86" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M86" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="S86" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T86" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="U86" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="W86" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X86">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>50</v>
       </c>
@@ -7228,31 +7259,31 @@
         <v>301</v>
       </c>
       <c r="J87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M87" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="S87" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T87" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="U87" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="W87" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>50</v>
       </c>
@@ -7272,31 +7303,31 @@
         <v>301</v>
       </c>
       <c r="J88" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M88" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="S88" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T88" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="U88" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="W88" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X88">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>50</v>
       </c>
@@ -7316,31 +7347,31 @@
         <v>301</v>
       </c>
       <c r="J89" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M89" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="S89" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T89" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="U89" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="W89" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X89">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>51</v>
       </c>
@@ -7360,31 +7391,31 @@
         <v>301</v>
       </c>
       <c r="J90" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M90" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="S90" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T90" t="s">
+        <v>871</v>
+      </c>
+      <c r="U90" t="s">
         <v>873</v>
       </c>
-      <c r="U90" t="s">
-        <v>875</v>
-      </c>
       <c r="W90" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X90">
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>51</v>
       </c>
@@ -7404,31 +7435,31 @@
         <v>301</v>
       </c>
       <c r="J91" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M91" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="S91" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T91" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="U91" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="W91" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>51</v>
       </c>
@@ -7448,31 +7479,31 @@
         <v>301</v>
       </c>
       <c r="J92" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M92" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="S92" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T92" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="U92" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="W92" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X92">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>51</v>
       </c>
@@ -7492,31 +7523,31 @@
         <v>301</v>
       </c>
       <c r="J93" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M93" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S93" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T93" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="U93" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="W93" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X93">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>52</v>
       </c>
@@ -7536,31 +7567,31 @@
         <v>304</v>
       </c>
       <c r="J94" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M94" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="S94" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T94" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="U94" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="W94" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="X94">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>52</v>
       </c>
@@ -7580,31 +7611,31 @@
         <v>304</v>
       </c>
       <c r="J95" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M95" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="S95" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T95" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="U95" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="W95" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="X95">
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>52</v>
       </c>
@@ -7624,31 +7655,31 @@
         <v>304</v>
       </c>
       <c r="J96" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="M96" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="S96" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T96" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="U96" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W96" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="X96">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -7668,31 +7699,31 @@
         <v>322</v>
       </c>
       <c r="J97" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M97" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="S97" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T97" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U97" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W97" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -7712,31 +7743,31 @@
         <v>295</v>
       </c>
       <c r="J98" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M98" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="S98" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T98" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="U98" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="W98" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X98">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -7756,31 +7787,31 @@
         <v>323</v>
       </c>
       <c r="J99" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M99" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="S99" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T99" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="U99" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="W99" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X99">
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>54</v>
       </c>
@@ -7800,31 +7831,31 @@
         <v>294</v>
       </c>
       <c r="J100" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M100" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="S100" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T100" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="U100" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="W100" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X100">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>54</v>
       </c>
@@ -7844,31 +7875,31 @@
         <v>294</v>
       </c>
       <c r="J101" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M101" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="S101" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T101" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="U101" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="W101" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X101">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>55</v>
       </c>
@@ -7888,31 +7919,31 @@
         <v>304</v>
       </c>
       <c r="J102" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M102" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="S102" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T102" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="U102" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="W102" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X102">
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -7928,35 +7959,32 @@
       <c r="H103" t="s">
         <v>261</v>
       </c>
-      <c r="I103" t="s">
-        <v>324</v>
-      </c>
       <c r="J103" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="M103" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="S103" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T103" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="U103" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="W103" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X103">
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>55</v>
       </c>
@@ -7976,31 +8004,31 @@
         <v>294</v>
       </c>
       <c r="J104" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M104" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S104" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T104" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="U104" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="W104" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X104">
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>56</v>
       </c>
@@ -8026,34 +8054,34 @@
         <v>296</v>
       </c>
       <c r="J105" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="M105" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="Q105" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="S105" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T105" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="U105" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="W105" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>56</v>
       </c>
@@ -8079,34 +8107,34 @@
         <v>301</v>
       </c>
       <c r="J106" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M106" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="Q106" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="S106" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T106" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="U106" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="W106" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X106">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>56</v>
       </c>
@@ -8132,34 +8160,34 @@
         <v>304</v>
       </c>
       <c r="J107" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M107" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="Q107" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="S107" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T107" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="U107" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="W107" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>56</v>
       </c>
@@ -8185,34 +8213,34 @@
         <v>296</v>
       </c>
       <c r="J108" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M108" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="Q108" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="S108" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T108" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="U108" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W108" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X108">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>57</v>
       </c>
@@ -8232,31 +8260,31 @@
         <v>301</v>
       </c>
       <c r="J109" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M109" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="S109" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T109" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="U109" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="W109" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X109">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>57</v>
       </c>
@@ -8276,31 +8304,31 @@
         <v>298</v>
       </c>
       <c r="J110" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M110" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="S110" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T110" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="U110" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="W110" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X110">
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>57</v>
       </c>
@@ -8317,34 +8345,34 @@
         <v>264</v>
       </c>
       <c r="I111" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J111" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="M111" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="S111" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T111" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="U111" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="W111" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X111">
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>57</v>
       </c>
@@ -8364,31 +8392,31 @@
         <v>294</v>
       </c>
       <c r="J112" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M112" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="S112" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T112" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="U112" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="W112" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X112">
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>58</v>
       </c>
@@ -8405,34 +8433,34 @@
         <v>265</v>
       </c>
       <c r="I113" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J113" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M113" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="S113" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T113" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="U113" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="W113" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X113">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>58</v>
       </c>
@@ -8452,31 +8480,31 @@
         <v>302</v>
       </c>
       <c r="J114" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M114" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="S114" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T114" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="U114" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W114" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X114">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>58</v>
       </c>
@@ -8493,34 +8521,34 @@
         <v>266</v>
       </c>
       <c r="I115" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J115" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M115" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="S115" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T115" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="U115" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="W115" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X115">
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>58</v>
       </c>
@@ -8540,34 +8568,34 @@
         <v>302</v>
       </c>
       <c r="J116" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M116" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="Q116" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="S116" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T116" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="U116" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="W116" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X116">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>59</v>
       </c>
@@ -8587,31 +8615,31 @@
         <v>299</v>
       </c>
       <c r="J117" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M117" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="S117" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T117" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="U117" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="W117" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X117">
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>59</v>
       </c>
@@ -8631,31 +8659,31 @@
         <v>301</v>
       </c>
       <c r="J118" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M118" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="S118" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T118" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="U118" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="W118" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>59</v>
       </c>
@@ -8675,31 +8703,31 @@
         <v>301</v>
       </c>
       <c r="J119" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M119" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="S119" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T119" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="U119" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="W119" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X119">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>59</v>
       </c>
@@ -8719,31 +8747,31 @@
         <v>301</v>
       </c>
       <c r="J120" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M120" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="S120" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T120" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U120" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="W120" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X120">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>60</v>
       </c>
@@ -8760,34 +8788,34 @@
         <v>268</v>
       </c>
       <c r="I121" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J121" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M121" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="S121" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T121" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="U121" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="W121" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X121">
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>60</v>
       </c>
@@ -8807,31 +8835,31 @@
         <v>317</v>
       </c>
       <c r="J122" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M122" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="S122" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T122" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="U122" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="W122" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X122">
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>61</v>
       </c>
@@ -8848,34 +8876,34 @@
         <v>270</v>
       </c>
       <c r="I123" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J123" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M123" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="S123" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T123" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="U123" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="W123" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X123">
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>61</v>
       </c>
@@ -8895,28 +8923,28 @@
         <v>296</v>
       </c>
       <c r="J124" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M124" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="Q124" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="S124" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="W124" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -8936,31 +8964,31 @@
         <v>317</v>
       </c>
       <c r="J125" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M125" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="S125" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T125" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="U125" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="W125" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X125">
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>62</v>
       </c>
@@ -8976,35 +9004,32 @@
       <c r="H126" t="s">
         <v>254</v>
       </c>
-      <c r="I126" t="s">
-        <v>321</v>
-      </c>
       <c r="J126" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M126" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="S126" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T126" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="U126" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="W126" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X126">
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>62</v>
       </c>
@@ -9020,35 +9045,32 @@
       <c r="H127" t="s">
         <v>273</v>
       </c>
-      <c r="I127" t="s">
-        <v>321</v>
-      </c>
       <c r="J127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M127" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="S127" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T127" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="U127" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W127" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X127">
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>62</v>
       </c>
@@ -9065,34 +9087,34 @@
         <v>274</v>
       </c>
       <c r="I128" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J128" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="M128" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="S128" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T128" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="U128" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="W128" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X128">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>63</v>
       </c>
@@ -9112,31 +9134,31 @@
         <v>301</v>
       </c>
       <c r="J129" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M129" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="S129" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T129" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="U129" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="W129" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X129">
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>63</v>
       </c>
@@ -9153,34 +9175,34 @@
         <v>217</v>
       </c>
       <c r="I130" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J130" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="M130" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S130" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T130" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="U130" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="W130" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X130">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>64</v>
       </c>
@@ -9197,37 +9219,37 @@
         <v>275</v>
       </c>
       <c r="I131" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J131" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M131" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="Q131" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="S131" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="T131" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="U131" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="W131" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>64</v>
       </c>
@@ -9244,37 +9266,37 @@
         <v>276</v>
       </c>
       <c r="I132" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J132" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M132" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="Q132" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="S132" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="T132" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="U132" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="W132" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X132">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>64</v>
       </c>
@@ -9294,34 +9316,34 @@
         <v>302</v>
       </c>
       <c r="J133" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M133" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="Q133" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="S133" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T133" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="U133" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="W133" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X133">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>64</v>
       </c>
@@ -9341,34 +9363,34 @@
         <v>302</v>
       </c>
       <c r="J134" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M134" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="Q134" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="S134" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T134" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="U134" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="W134" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X134">
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>46</v>
       </c>
@@ -9385,34 +9407,34 @@
         <v>277</v>
       </c>
       <c r="I135" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J135" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M135" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="S135" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T135" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="U135" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="W135" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X135">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>46</v>
       </c>
@@ -9429,34 +9451,34 @@
         <v>277</v>
       </c>
       <c r="I136" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J136" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M136" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="S136" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T136" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="U136" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="W136" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X136">
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>46</v>
       </c>
@@ -9476,31 +9498,31 @@
         <v>302</v>
       </c>
       <c r="J137" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M137" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="S137" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T137" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="U137" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="W137" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X137">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>46</v>
       </c>
@@ -9520,31 +9542,31 @@
         <v>302</v>
       </c>
       <c r="J138" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M138" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="S138" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T138" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="U138" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="W138" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X138">
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>54</v>
       </c>
@@ -9564,31 +9586,31 @@
         <v>294</v>
       </c>
       <c r="J139" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M139" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="S139" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T139" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="U139" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="W139" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X139">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>54</v>
       </c>
@@ -9608,31 +9630,31 @@
         <v>294</v>
       </c>
       <c r="J140" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M140" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="S140" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T140" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="U140" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="W140" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X140">
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>54</v>
       </c>
@@ -9652,31 +9674,31 @@
         <v>295</v>
       </c>
       <c r="J141" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M141" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="S141" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T141" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="U141" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="W141" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X141">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>65</v>
       </c>
@@ -9693,34 +9715,34 @@
         <v>280</v>
       </c>
       <c r="I142" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J142" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M142" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="S142" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T142" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="U142" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="W142" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X142">
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>65</v>
       </c>
@@ -9737,34 +9759,34 @@
         <v>238</v>
       </c>
       <c r="I143" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J143" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M143" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="S143" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T143" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="U143" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="W143" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X143">
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>65</v>
       </c>
@@ -9781,34 +9803,34 @@
         <v>236</v>
       </c>
       <c r="I144" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J144" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M144" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="S144" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T144" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="U144" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="W144" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X144">
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>65</v>
       </c>
@@ -9825,34 +9847,34 @@
         <v>227</v>
       </c>
       <c r="I145" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J145" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M145" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="S145" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T145" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="U145" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="W145" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X145">
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>66</v>
       </c>
@@ -9872,31 +9894,31 @@
         <v>301</v>
       </c>
       <c r="J146" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M146" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="S146" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T146" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="U146" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="W146" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X146">
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>66</v>
       </c>
@@ -9916,31 +9938,31 @@
         <v>301</v>
       </c>
       <c r="J147" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M147" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="S147" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T147" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="U147" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="W147" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X147">
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>66</v>
       </c>
@@ -9960,31 +9982,31 @@
         <v>302</v>
       </c>
       <c r="J148" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M148" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="S148" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T148" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="U148" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="W148" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X148">
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:24">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>66</v>
       </c>
@@ -10004,31 +10026,31 @@
         <v>319</v>
       </c>
       <c r="J149" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M149" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="S149" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T149" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="U149" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="W149" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X149">
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:24">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>32</v>
       </c>
@@ -10048,31 +10070,31 @@
         <v>304</v>
       </c>
       <c r="J150" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M150" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="S150" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T150" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="U150" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="W150" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X150">
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>32</v>
       </c>
@@ -10092,31 +10114,31 @@
         <v>304</v>
       </c>
       <c r="J151" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M151" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="S151" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T151" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="U151" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="W151" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X151">
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>32</v>
       </c>
@@ -10136,31 +10158,31 @@
         <v>294</v>
       </c>
       <c r="J152" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M152" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="S152" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T152" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="U152" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="W152" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X152">
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:24">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>67</v>
       </c>
@@ -10180,31 +10202,31 @@
         <v>304</v>
       </c>
       <c r="J153" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M153" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="S153" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T153" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="U153" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="W153" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X153">
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:24">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>67</v>
       </c>
@@ -10224,31 +10246,31 @@
         <v>301</v>
       </c>
       <c r="J154" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M154" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="S154" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T154" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="U154" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="W154" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X154">
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>67</v>
       </c>
@@ -10268,31 +10290,31 @@
         <v>304</v>
       </c>
       <c r="J155" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M155" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="S155" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T155" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="U155" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="W155" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X155">
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>67</v>
       </c>
@@ -10312,31 +10334,31 @@
         <v>304</v>
       </c>
       <c r="J156" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M156" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="S156" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T156" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="U156" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="W156" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="X156">
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>54</v>
       </c>
@@ -10353,34 +10375,34 @@
         <v>229</v>
       </c>
       <c r="I157" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J157" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="M157" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="S157" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T157" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="U157" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="W157" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X157">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:24">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>54</v>
       </c>
@@ -10400,31 +10422,31 @@
         <v>295</v>
       </c>
       <c r="J158" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M158" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="S158" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T158" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="U158" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="W158" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X158">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:24">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>54</v>
       </c>
@@ -10441,31 +10463,31 @@
         <v>282</v>
       </c>
       <c r="J159" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M159" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="S159" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T159" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="U159" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="W159" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X159">
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:24">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>68</v>
       </c>
@@ -10485,31 +10507,31 @@
         <v>304</v>
       </c>
       <c r="J160" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M160" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="S160" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T160" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="U160" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="W160" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X160">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:24">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>68</v>
       </c>
@@ -10526,34 +10548,34 @@
         <v>154</v>
       </c>
       <c r="I161" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J161" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M161" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="S161" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T161" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="U161" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="W161" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X161">
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:24">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>68</v>
       </c>
@@ -10573,31 +10595,31 @@
         <v>301</v>
       </c>
       <c r="J162" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M162" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="S162" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T162" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="U162" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="W162" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X162">
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:24">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>68</v>
       </c>
@@ -10614,34 +10636,34 @@
         <v>238</v>
       </c>
       <c r="I163" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J163" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M163" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="S163" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T163" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="U163" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="W163" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X163">
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:24">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>28</v>
       </c>
@@ -10661,31 +10683,31 @@
         <v>294</v>
       </c>
       <c r="J164" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M164" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="S164" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T164" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="U164" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="W164" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X164">
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:24">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>28</v>
       </c>
@@ -10705,31 +10727,31 @@
         <v>298</v>
       </c>
       <c r="J165" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M165" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="S165" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T165" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="U165" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="W165" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X165">
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:24">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>28</v>
       </c>
@@ -10749,31 +10771,31 @@
         <v>294</v>
       </c>
       <c r="J166" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M166" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="S166" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T166" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="U166" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="W166" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X166">
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:24">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>69</v>
       </c>
@@ -10796,34 +10818,34 @@
         <v>295</v>
       </c>
       <c r="J167" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M167" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="Q167" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="S167" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T167" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="U167" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="W167" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X167">
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:24">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>69</v>
       </c>
@@ -10846,31 +10868,31 @@
         <v>301</v>
       </c>
       <c r="J168" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M168" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="S168" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T168" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="U168" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="W168" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X168">
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:24">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>69</v>
       </c>
@@ -10890,34 +10912,34 @@
         <v>283</v>
       </c>
       <c r="I169" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J169" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M169" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="S169" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T169" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="U169" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="W169" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X169">
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:24">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>69</v>
       </c>
@@ -10940,34 +10962,34 @@
         <v>294</v>
       </c>
       <c r="J170" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M170" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Q170" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="S170" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T170" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="U170" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="W170" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:24">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>69</v>
       </c>
@@ -10990,31 +11012,31 @@
         <v>304</v>
       </c>
       <c r="J171" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M171" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="N171" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="S171" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T171" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="U171" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="W171" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X171">
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:24">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>69</v>
       </c>
@@ -11037,31 +11059,31 @@
         <v>294</v>
       </c>
       <c r="J172" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M172" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="S172" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T172" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="U172" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="W172" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X172">
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:24">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>48</v>
       </c>
@@ -11081,31 +11103,31 @@
         <v>298</v>
       </c>
       <c r="J173" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M173" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="S173" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T173" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="U173" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="W173" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X173">
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:24">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>48</v>
       </c>
@@ -11125,31 +11147,31 @@
         <v>294</v>
       </c>
       <c r="J174" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M174" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N174" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="S174" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T174" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="U174" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="W174" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X174">
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:24">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>48</v>
       </c>
@@ -11169,31 +11191,31 @@
         <v>295</v>
       </c>
       <c r="J175" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M175" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N175" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="S175" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T175" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="U175" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="W175" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X175">
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:24">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>70</v>
       </c>
@@ -11213,31 +11235,31 @@
         <v>294</v>
       </c>
       <c r="J176" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M176" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="S176" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T176" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="U176" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="W176" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X176">
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:24">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>70</v>
       </c>
@@ -11257,31 +11279,31 @@
         <v>301</v>
       </c>
       <c r="J177" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M177" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="S177" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T177" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U177" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="W177" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X177">
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:24">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>70</v>
       </c>
@@ -11301,31 +11323,31 @@
         <v>295</v>
       </c>
       <c r="J178" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M178" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="S178" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T178" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="U178" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="W178" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X178">
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:24">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>71</v>
       </c>
@@ -11345,34 +11367,34 @@
         <v>302</v>
       </c>
       <c r="J179" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M179" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="Q179" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="S179" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T179" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="U179" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="W179" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X179">
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:24">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>71</v>
       </c>
@@ -11392,34 +11414,34 @@
         <v>304</v>
       </c>
       <c r="J180" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M180" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="Q180" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="S180" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T180" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="U180" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="W180" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X180">
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:24">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>71</v>
       </c>
@@ -11439,34 +11461,34 @@
         <v>296</v>
       </c>
       <c r="J181" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M181" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Q181" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="S181" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T181" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="U181" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="W181" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X181">
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:24">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>71</v>
       </c>
@@ -11486,34 +11508,34 @@
         <v>302</v>
       </c>
       <c r="J182" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M182" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="Q182" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="S182" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T182" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="U182" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="W182" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="X182">
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:24">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>72</v>
       </c>
@@ -11533,34 +11555,34 @@
         <v>294</v>
       </c>
       <c r="J183" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M183" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="Q183" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="S183" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T183" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="U183" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="W183" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X183">
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:24">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>72</v>
       </c>
@@ -11580,34 +11602,34 @@
         <v>295</v>
       </c>
       <c r="J184" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M184" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="Q184" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="S184" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T184" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="U184" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="W184" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X184">
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:24">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>72</v>
       </c>
@@ -11627,34 +11649,34 @@
         <v>295</v>
       </c>
       <c r="J185" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M185" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="Q185" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="S185" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T185" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="U185" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="W185" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X185">
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:24">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>72</v>
       </c>
@@ -11671,37 +11693,37 @@
         <v>288</v>
       </c>
       <c r="I186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J186" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M186" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="Q186" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="S186" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T186" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="U186" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="W186" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="X186">
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:24">
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>73</v>
       </c>
@@ -11721,31 +11743,31 @@
         <v>302</v>
       </c>
       <c r="J187" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M187" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="S187" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T187" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="U187" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="W187" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X187">
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:24">
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>73</v>
       </c>
@@ -11765,31 +11787,31 @@
         <v>309</v>
       </c>
       <c r="J188" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M188" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="S188" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T188" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="U188" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="W188" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X188">
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:24">
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>73</v>
       </c>
@@ -11809,31 +11831,31 @@
         <v>301</v>
       </c>
       <c r="J189" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M189" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="S189" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T189" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="U189" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="W189" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X189">
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:24">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>73</v>
       </c>
@@ -11853,31 +11875,31 @@
         <v>301</v>
       </c>
       <c r="J190" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M190" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="S190" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T190" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="U190" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="W190" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="X190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:24">
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>74</v>
       </c>
@@ -11903,31 +11925,31 @@
         <v>296</v>
       </c>
       <c r="J191" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M191" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="S191" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T191" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="U191" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="W191" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X191">
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:24">
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>74</v>
       </c>
@@ -11953,31 +11975,31 @@
         <v>296</v>
       </c>
       <c r="J192" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M192" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="S192" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="T192" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="U192" t="s">
+        <v>998</v>
+      </c>
+      <c r="W192" t="s">
         <v>1000</v>
       </c>
-      <c r="W192" t="s">
-        <v>1002</v>
-      </c>
       <c r="X192">
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:24">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>74</v>
       </c>
@@ -12003,25 +12025,31 @@
         <v>296</v>
       </c>
       <c r="J193" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M193" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="S193" t="s">
-        <v>804</v>
+        <v>802</v>
+      </c>
+      <c r="T193">
+        <v>123</v>
+      </c>
+      <c r="U193">
+        <v>89</v>
       </c>
       <c r="W193" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X193">
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:24">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>74</v>
       </c>
@@ -12044,22 +12072,28 @@
         <v>293</v>
       </c>
       <c r="I194" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J194" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M194" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="S194" t="s">
-        <v>804</v>
+        <v>802</v>
+      </c>
+      <c r="T194">
+        <v>533</v>
+      </c>
+      <c r="U194">
+        <v>342</v>
       </c>
       <c r="W194" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="X194">
         <v>3</v>
@@ -12067,199 +12101,199 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
-    <hyperlink ref="N110" r:id="rId109"/>
-    <hyperlink ref="N111" r:id="rId110"/>
-    <hyperlink ref="N112" r:id="rId111"/>
-    <hyperlink ref="N113" r:id="rId112"/>
-    <hyperlink ref="N114" r:id="rId113"/>
-    <hyperlink ref="N115" r:id="rId114"/>
-    <hyperlink ref="N116" r:id="rId115"/>
-    <hyperlink ref="N117" r:id="rId116"/>
-    <hyperlink ref="N118" r:id="rId117"/>
-    <hyperlink ref="N119" r:id="rId118"/>
-    <hyperlink ref="N120" r:id="rId119"/>
-    <hyperlink ref="N121" r:id="rId120"/>
-    <hyperlink ref="N122" r:id="rId121"/>
-    <hyperlink ref="N123" r:id="rId122"/>
-    <hyperlink ref="N124" r:id="rId123"/>
-    <hyperlink ref="N125" r:id="rId124"/>
-    <hyperlink ref="N126" r:id="rId125"/>
-    <hyperlink ref="N127" r:id="rId126"/>
-    <hyperlink ref="N128" r:id="rId127"/>
-    <hyperlink ref="N129" r:id="rId128"/>
-    <hyperlink ref="N130" r:id="rId129"/>
-    <hyperlink ref="N131" r:id="rId130"/>
-    <hyperlink ref="N132" r:id="rId131"/>
-    <hyperlink ref="N133" r:id="rId132"/>
-    <hyperlink ref="N134" r:id="rId133"/>
-    <hyperlink ref="N135" r:id="rId134"/>
-    <hyperlink ref="N136" r:id="rId135"/>
-    <hyperlink ref="N137" r:id="rId136"/>
-    <hyperlink ref="N138" r:id="rId137"/>
-    <hyperlink ref="N139" r:id="rId138"/>
-    <hyperlink ref="N140" r:id="rId139"/>
-    <hyperlink ref="N141" r:id="rId140"/>
-    <hyperlink ref="N142" r:id="rId141"/>
-    <hyperlink ref="N143" r:id="rId142"/>
-    <hyperlink ref="N144" r:id="rId143"/>
-    <hyperlink ref="N145" r:id="rId144"/>
-    <hyperlink ref="N146" r:id="rId145"/>
-    <hyperlink ref="N147" r:id="rId146"/>
-    <hyperlink ref="N148" r:id="rId147"/>
-    <hyperlink ref="N149" r:id="rId148"/>
-    <hyperlink ref="N150" r:id="rId149"/>
-    <hyperlink ref="N151" r:id="rId150"/>
-    <hyperlink ref="N152" r:id="rId151"/>
-    <hyperlink ref="N153" r:id="rId152"/>
-    <hyperlink ref="N154" r:id="rId153"/>
-    <hyperlink ref="N155" r:id="rId154"/>
-    <hyperlink ref="N156" r:id="rId155"/>
-    <hyperlink ref="N157" r:id="rId156"/>
-    <hyperlink ref="N158" r:id="rId157"/>
-    <hyperlink ref="N159" r:id="rId158"/>
-    <hyperlink ref="N160" r:id="rId159"/>
-    <hyperlink ref="N161" r:id="rId160"/>
-    <hyperlink ref="N162" r:id="rId161"/>
-    <hyperlink ref="N163" r:id="rId162"/>
-    <hyperlink ref="N164" r:id="rId163"/>
-    <hyperlink ref="N165" r:id="rId164"/>
-    <hyperlink ref="N166" r:id="rId165"/>
-    <hyperlink ref="N167" r:id="rId166"/>
-    <hyperlink ref="N168" r:id="rId167"/>
-    <hyperlink ref="N169" r:id="rId168"/>
-    <hyperlink ref="N170" r:id="rId169"/>
-    <hyperlink ref="N171" r:id="rId170"/>
-    <hyperlink ref="N172" r:id="rId171"/>
-    <hyperlink ref="N173" r:id="rId172"/>
-    <hyperlink ref="N174" r:id="rId173"/>
-    <hyperlink ref="N175" r:id="rId174"/>
-    <hyperlink ref="N176" r:id="rId175"/>
-    <hyperlink ref="N177" r:id="rId176"/>
-    <hyperlink ref="N178" r:id="rId177"/>
-    <hyperlink ref="N179" r:id="rId178"/>
-    <hyperlink ref="N180" r:id="rId179"/>
-    <hyperlink ref="N181" r:id="rId180"/>
-    <hyperlink ref="N182" r:id="rId181"/>
-    <hyperlink ref="N183" r:id="rId182"/>
-    <hyperlink ref="N184" r:id="rId183"/>
-    <hyperlink ref="N185" r:id="rId184"/>
-    <hyperlink ref="N186" r:id="rId185"/>
-    <hyperlink ref="N187" r:id="rId186"/>
-    <hyperlink ref="N188" r:id="rId187"/>
-    <hyperlink ref="N189" r:id="rId188"/>
-    <hyperlink ref="N190" r:id="rId189"/>
-    <hyperlink ref="N191" r:id="rId190"/>
-    <hyperlink ref="N192" r:id="rId191"/>
-    <hyperlink ref="N193" r:id="rId192"/>
-    <hyperlink ref="N194" r:id="rId193"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="N111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="N113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="N117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="N121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="N123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="N125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="N126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="N127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="N128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="N129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="N130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="N131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="N132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="N133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="N134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="N135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="N136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="N137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="N138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="N139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="N140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="N141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="N142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="N143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="N144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="N145" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="N146" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="N147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="N148" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="N149" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="N150" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="N151" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="N152" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="N153" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="N154" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="N155" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="N156" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="N157" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="N158" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="N159" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="N160" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="N161" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="N162" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="N163" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="N164" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="N165" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="N166" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="N167" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="N168" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="N169" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="N170" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="N171" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="N172" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="N173" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="N174" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="N175" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="N176" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="N177" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="N178" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="N179" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="N180" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="N181" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="N182" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="N183" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="N184" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="N185" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="N186" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="N187" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="N188" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="N189" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="N190" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="N191" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="N192" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="N193" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="N194" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -32,7 +32,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +67,11 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3465,8 +3471,10 @@
           <t>de CHAMPAIGNE</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1950</v>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1506770-F2E6-4D6C-A897-F67517AFE157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="345" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1506770-F2E6-4D6C-A897-F67517AFE157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A35C7E-998D-4824-A37B-49CBD0B9EC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="345" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2754" uniqueCount="1118">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1877,9 +1877,6 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Supper_at_Emmaus-Caravaggio_%281601%29.jpg/1280px-Supper_at_Emmaus-Caravaggio_%281601%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Galleria Borghese</t>
   </si>
   <si>
     <t>"David avec la tête de Goliath"</t>
@@ -4178,7 +4175,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="J11" t="s">
         <v>76</v>
@@ -6681,7 +6678,7 @@
         <v>327</v>
       </c>
       <c r="F76" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="J76" t="s">
         <v>328</v>
@@ -7140,7 +7137,7 @@
         <v>367</v>
       </c>
       <c r="F88" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="J88" t="s">
         <v>368</v>
@@ -7792,7 +7789,7 @@
         <v>440</v>
       </c>
       <c r="F105" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J105" t="s">
         <v>441</v>
@@ -7827,13 +7824,13 @@
         <v>445</v>
       </c>
       <c r="D106" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E106" t="s">
         <v>446</v>
       </c>
       <c r="F106" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="J106" t="s">
         <v>447</v>
@@ -7956,7 +7953,7 @@
         <v>457</v>
       </c>
       <c r="F109" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="J109" t="s">
         <v>285</v>
@@ -9533,16 +9530,16 @@
         <v>53</v>
       </c>
       <c r="F149" t="s">
+        <v>70</v>
+      </c>
+      <c r="J149" t="s">
         <v>619</v>
       </c>
-      <c r="J149" t="s">
+      <c r="K149" t="s">
         <v>620</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>622</v>
       </c>
       <c r="R149" t="s">
         <v>30</v>
@@ -9562,13 +9559,13 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>622</v>
+      </c>
+      <c r="B150" t="s">
         <v>623</v>
       </c>
-      <c r="B150" t="s">
+      <c r="D150" t="s">
         <v>624</v>
-      </c>
-      <c r="D150" t="s">
-        <v>625</v>
       </c>
       <c r="E150" t="s">
         <v>88</v>
@@ -9577,10 +9574,10 @@
         <v>89</v>
       </c>
       <c r="J150" t="s">
+        <v>625</v>
+      </c>
+      <c r="L150" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="R150" t="s">
         <v>30</v>
@@ -9600,10 +9597,10 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>622</v>
+      </c>
+      <c r="B151" t="s">
         <v>623</v>
-      </c>
-      <c r="B151" t="s">
-        <v>624</v>
       </c>
       <c r="D151" t="s">
         <v>233</v>
@@ -9615,10 +9612,10 @@
         <v>97</v>
       </c>
       <c r="J151" t="s">
+        <v>627</v>
+      </c>
+      <c r="L151" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>629</v>
       </c>
       <c r="R151" t="s">
         <v>30</v>
@@ -9638,25 +9635,25 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>622</v>
+      </c>
+      <c r="B152" t="s">
         <v>623</v>
       </c>
-      <c r="B152" t="s">
-        <v>624</v>
-      </c>
       <c r="D152" t="s">
+        <v>629</v>
+      </c>
+      <c r="E152" t="s">
         <v>630</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>631</v>
       </c>
-      <c r="F152" t="s">
+      <c r="J152" t="s">
         <v>632</v>
       </c>
-      <c r="J152" t="s">
+      <c r="L152" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="L152" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="R152" t="s">
         <v>30</v>
@@ -9676,13 +9673,13 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>622</v>
+      </c>
+      <c r="B153" t="s">
         <v>623</v>
       </c>
-      <c r="B153" t="s">
-        <v>624</v>
-      </c>
       <c r="D153" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E153" t="s">
         <v>26</v>
@@ -9691,10 +9688,10 @@
         <v>27</v>
       </c>
       <c r="J153" t="s">
+        <v>634</v>
+      </c>
+      <c r="L153" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="R153" t="s">
         <v>30</v>
@@ -9714,28 +9711,28 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>636</v>
+      </c>
+      <c r="B154" t="s">
         <v>637</v>
       </c>
-      <c r="B154" t="s">
+      <c r="D154" t="s">
         <v>638</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>639</v>
       </c>
-      <c r="E154" t="s">
+      <c r="F154" t="s">
         <v>640</v>
       </c>
-      <c r="F154" t="s">
+      <c r="J154" t="s">
         <v>641</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>642</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" s="1" t="s">
         <v>643</v>
-      </c>
-      <c r="L154" s="1" t="s">
-        <v>644</v>
       </c>
       <c r="R154" t="s">
         <v>30</v>
@@ -9755,10 +9752,10 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>636</v>
+      </c>
+      <c r="B155" t="s">
         <v>637</v>
-      </c>
-      <c r="B155" t="s">
-        <v>638</v>
       </c>
       <c r="D155" t="s">
         <v>472</v>
@@ -9770,13 +9767,13 @@
         <v>121</v>
       </c>
       <c r="J155" t="s">
+        <v>644</v>
+      </c>
+      <c r="K155" t="s">
         <v>645</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="L155" s="1" t="s">
-        <v>647</v>
       </c>
       <c r="R155" t="s">
         <v>30</v>
@@ -9796,28 +9793,28 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>636</v>
+      </c>
+      <c r="B156" t="s">
         <v>637</v>
       </c>
-      <c r="B156" t="s">
-        <v>638</v>
-      </c>
       <c r="D156" t="s">
+        <v>647</v>
+      </c>
+      <c r="E156" t="s">
+        <v>639</v>
+      </c>
+      <c r="F156" t="s">
+        <v>640</v>
+      </c>
+      <c r="J156" t="s">
         <v>648</v>
       </c>
-      <c r="E156" t="s">
-        <v>640</v>
-      </c>
-      <c r="F156" t="s">
-        <v>641</v>
-      </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>649</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="L156" s="1" t="s">
-        <v>651</v>
       </c>
       <c r="R156" t="s">
         <v>30</v>
@@ -9837,13 +9834,13 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>636</v>
+      </c>
+      <c r="B157" t="s">
         <v>637</v>
       </c>
-      <c r="B157" t="s">
-        <v>638</v>
-      </c>
       <c r="D157" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E157" t="s">
         <v>48</v>
@@ -9852,13 +9849,13 @@
         <v>121</v>
       </c>
       <c r="J157" t="s">
+        <v>652</v>
+      </c>
+      <c r="K157" t="s">
         <v>653</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="L157" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="R157" t="s">
         <v>30</v>
@@ -9878,13 +9875,13 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>636</v>
+      </c>
+      <c r="B158" t="s">
         <v>637</v>
       </c>
-      <c r="B158" t="s">
-        <v>638</v>
-      </c>
       <c r="D158" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E158" t="s">
         <v>88</v>
@@ -9893,13 +9890,13 @@
         <v>89</v>
       </c>
       <c r="J158" t="s">
+        <v>656</v>
+      </c>
+      <c r="K158" t="s">
         <v>657</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="L158" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="R158" t="s">
         <v>30</v>
@@ -9919,13 +9916,13 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>636</v>
+      </c>
+      <c r="B159" t="s">
         <v>637</v>
       </c>
-      <c r="B159" t="s">
-        <v>638</v>
-      </c>
       <c r="D159" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E159" t="s">
         <v>48</v>
@@ -9934,13 +9931,13 @@
         <v>121</v>
       </c>
       <c r="J159" t="s">
+        <v>660</v>
+      </c>
+      <c r="K159" t="s">
         <v>661</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="L159" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="R159" t="s">
         <v>30</v>
@@ -9960,13 +9957,13 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>636</v>
+      </c>
+      <c r="B160" t="s">
         <v>637</v>
       </c>
-      <c r="B160" t="s">
-        <v>638</v>
-      </c>
       <c r="D160" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E160" t="s">
         <v>48</v>
@@ -9975,13 +9972,13 @@
         <v>121</v>
       </c>
       <c r="J160" t="s">
+        <v>664</v>
+      </c>
+      <c r="K160" t="s">
         <v>665</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" s="1" t="s">
         <v>666</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>667</v>
       </c>
       <c r="R160" t="s">
         <v>30</v>
@@ -10001,10 +9998,10 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>636</v>
+      </c>
+      <c r="B161" t="s">
         <v>637</v>
-      </c>
-      <c r="B161" t="s">
-        <v>638</v>
       </c>
       <c r="D161" t="s">
         <v>201</v>
@@ -10016,13 +10013,13 @@
         <v>246</v>
       </c>
       <c r="J161" t="s">
+        <v>667</v>
+      </c>
+      <c r="K161" t="s">
         <v>668</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="L161" s="1" t="s">
-        <v>670</v>
       </c>
       <c r="R161" t="s">
         <v>30</v>
@@ -10042,13 +10039,13 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>670</v>
+      </c>
+      <c r="B162" t="s">
         <v>671</v>
       </c>
-      <c r="B162" t="s">
+      <c r="D162" t="s">
         <v>672</v>
-      </c>
-      <c r="D162" t="s">
-        <v>673</v>
       </c>
       <c r="E162" t="s">
         <v>101</v>
@@ -10057,10 +10054,10 @@
         <v>102</v>
       </c>
       <c r="J162" t="s">
+        <v>673</v>
+      </c>
+      <c r="L162" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="L162" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="R162" t="s">
         <v>30</v>
@@ -10080,10 +10077,10 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>670</v>
+      </c>
+      <c r="B163" t="s">
         <v>671</v>
-      </c>
-      <c r="B163" t="s">
-        <v>672</v>
       </c>
       <c r="D163" t="s">
         <v>131</v>
@@ -10095,10 +10092,10 @@
         <v>89</v>
       </c>
       <c r="J163" t="s">
+        <v>675</v>
+      </c>
+      <c r="L163" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="R163" t="s">
         <v>30</v>
@@ -10118,10 +10115,10 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>670</v>
+      </c>
+      <c r="B164" t="s">
         <v>671</v>
-      </c>
-      <c r="B164" t="s">
-        <v>672</v>
       </c>
       <c r="D164" t="s">
         <v>244</v>
@@ -10133,10 +10130,10 @@
         <v>89</v>
       </c>
       <c r="J164" t="s">
+        <v>677</v>
+      </c>
+      <c r="L164" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>679</v>
       </c>
       <c r="R164" t="s">
         <v>30</v>
@@ -10156,10 +10153,10 @@
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>670</v>
+      </c>
+      <c r="B165" t="s">
         <v>671</v>
-      </c>
-      <c r="B165" t="s">
-        <v>672</v>
       </c>
       <c r="D165" t="s">
         <v>192</v>
@@ -10174,7 +10171,7 @@
         <v>71</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="R165" t="s">
         <v>30</v>
@@ -10194,13 +10191,13 @@
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>670</v>
+      </c>
+      <c r="B166" t="s">
         <v>671</v>
       </c>
-      <c r="B166" t="s">
-        <v>672</v>
-      </c>
       <c r="D166" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E166" t="s">
         <v>88</v>
@@ -10209,10 +10206,10 @@
         <v>89</v>
       </c>
       <c r="J166" t="s">
+        <v>681</v>
+      </c>
+      <c r="L166" s="1" t="s">
         <v>682</v>
-      </c>
-      <c r="L166" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="R166" t="s">
         <v>30</v>
@@ -10232,10 +10229,10 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>670</v>
+      </c>
+      <c r="B167" t="s">
         <v>671</v>
-      </c>
-      <c r="B167" t="s">
-        <v>672</v>
       </c>
       <c r="D167" t="s">
         <v>75</v>
@@ -10247,10 +10244,10 @@
         <v>89</v>
       </c>
       <c r="J167" t="s">
+        <v>683</v>
+      </c>
+      <c r="L167" s="1" t="s">
         <v>684</v>
-      </c>
-      <c r="L167" s="1" t="s">
-        <v>685</v>
       </c>
       <c r="R167" t="s">
         <v>30</v>
@@ -10270,13 +10267,13 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>670</v>
+      </c>
+      <c r="B168" t="s">
         <v>671</v>
       </c>
-      <c r="B168" t="s">
-        <v>672</v>
-      </c>
       <c r="D168" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E168" t="s">
         <v>88</v>
@@ -10285,10 +10282,10 @@
         <v>89</v>
       </c>
       <c r="J168" t="s">
+        <v>686</v>
+      </c>
+      <c r="L168" s="1" t="s">
         <v>687</v>
-      </c>
-      <c r="L168" s="1" t="s">
-        <v>688</v>
       </c>
       <c r="R168" t="s">
         <v>30</v>
@@ -10308,25 +10305,25 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>670</v>
+      </c>
+      <c r="B169" t="s">
         <v>671</v>
       </c>
-      <c r="B169" t="s">
-        <v>672</v>
-      </c>
       <c r="D169" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E169" t="s">
+        <v>688</v>
+      </c>
+      <c r="F169" t="s">
         <v>689</v>
       </c>
-      <c r="F169" t="s">
+      <c r="J169" t="s">
         <v>690</v>
       </c>
-      <c r="J169" t="s">
+      <c r="L169" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="L169" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="R169" t="s">
         <v>30</v>
@@ -10346,10 +10343,10 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>670</v>
+      </c>
+      <c r="B170" t="s">
         <v>671</v>
-      </c>
-      <c r="B170" t="s">
-        <v>672</v>
       </c>
       <c r="D170" t="s">
         <v>63</v>
@@ -10358,13 +10355,13 @@
         <v>96</v>
       </c>
       <c r="F170" t="s">
+        <v>692</v>
+      </c>
+      <c r="J170" t="s">
         <v>693</v>
       </c>
-      <c r="J170" t="s">
+      <c r="L170" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="L170" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="R170" t="s">
         <v>30</v>
@@ -10384,13 +10381,13 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>670</v>
+      </c>
+      <c r="B171" t="s">
         <v>671</v>
       </c>
-      <c r="B171" t="s">
-        <v>672</v>
-      </c>
       <c r="D171" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E171" t="s">
         <v>88</v>
@@ -10399,10 +10396,10 @@
         <v>89</v>
       </c>
       <c r="J171" t="s">
+        <v>696</v>
+      </c>
+      <c r="L171" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="L171" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="R171" t="s">
         <v>30</v>
@@ -10422,13 +10419,13 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>670</v>
+      </c>
+      <c r="B172" t="s">
         <v>671</v>
       </c>
-      <c r="B172" t="s">
-        <v>672</v>
-      </c>
       <c r="D172" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E172" t="s">
         <v>41</v>
@@ -10440,7 +10437,7 @@
         <v>285</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="R172" t="s">
         <v>30</v>
@@ -10460,13 +10457,13 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>670</v>
+      </c>
+      <c r="B173" t="s">
         <v>671</v>
       </c>
-      <c r="B173" t="s">
-        <v>672</v>
-      </c>
       <c r="D173" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E173" t="s">
         <v>88</v>
@@ -10475,10 +10472,10 @@
         <v>89</v>
       </c>
       <c r="J173" t="s">
+        <v>701</v>
+      </c>
+      <c r="L173" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="L173" s="1" t="s">
-        <v>703</v>
       </c>
       <c r="R173" t="s">
         <v>30</v>
@@ -10498,28 +10495,28 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>703</v>
+      </c>
+      <c r="B174" t="s">
         <v>704</v>
-      </c>
-      <c r="B174" t="s">
-        <v>705</v>
       </c>
       <c r="D174" t="s">
         <v>95</v>
       </c>
       <c r="E174" t="s">
+        <v>705</v>
+      </c>
+      <c r="F174" t="s">
         <v>706</v>
       </c>
-      <c r="F174" t="s">
+      <c r="J174" t="s">
         <v>707</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>708</v>
       </c>
-      <c r="K174" t="s">
+      <c r="L174" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="L174" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="R174" t="s">
         <v>30</v>
@@ -10539,10 +10536,10 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>703</v>
+      </c>
+      <c r="B175" t="s">
         <v>704</v>
-      </c>
-      <c r="B175" t="s">
-        <v>705</v>
       </c>
       <c r="D175" t="s">
         <v>537</v>
@@ -10551,16 +10548,16 @@
         <v>405</v>
       </c>
       <c r="F175" t="s">
+        <v>710</v>
+      </c>
+      <c r="J175" t="s">
         <v>711</v>
       </c>
-      <c r="J175" t="s">
+      <c r="K175" t="s">
         <v>712</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="L175" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="R175" t="s">
         <v>30</v>
@@ -10580,28 +10577,28 @@
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>703</v>
+      </c>
+      <c r="B176" t="s">
         <v>704</v>
       </c>
-      <c r="B176" t="s">
-        <v>705</v>
-      </c>
       <c r="D176" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E176" t="s">
         <v>405</v>
       </c>
       <c r="F176" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J176" t="s">
+        <v>715</v>
+      </c>
+      <c r="K176" t="s">
         <v>716</v>
       </c>
-      <c r="K176" t="s">
+      <c r="L176" s="1" t="s">
         <v>717</v>
-      </c>
-      <c r="L176" s="1" t="s">
-        <v>718</v>
       </c>
       <c r="R176" t="s">
         <v>30</v>
@@ -10621,28 +10618,28 @@
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>703</v>
+      </c>
+      <c r="B177" t="s">
         <v>704</v>
       </c>
-      <c r="B177" t="s">
-        <v>705</v>
-      </c>
       <c r="D177" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E177" t="s">
         <v>405</v>
       </c>
       <c r="F177" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J177" t="s">
+        <v>719</v>
+      </c>
+      <c r="K177" t="s">
         <v>720</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="L177" s="1" t="s">
-        <v>722</v>
       </c>
       <c r="R177" t="s">
         <v>30</v>
@@ -10662,28 +10659,28 @@
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>722</v>
+      </c>
+      <c r="B178" t="s">
         <v>723</v>
       </c>
-      <c r="B178" t="s">
+      <c r="D178" t="s">
         <v>724</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>725</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>726</v>
       </c>
-      <c r="F178" t="s">
+      <c r="J178" t="s">
         <v>727</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>728</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="1" t="s">
         <v>729</v>
-      </c>
-      <c r="L178" s="1" t="s">
-        <v>730</v>
       </c>
       <c r="R178" t="s">
         <v>30</v>
@@ -10703,34 +10700,34 @@
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>722</v>
+      </c>
+      <c r="B179" t="s">
         <v>723</v>
       </c>
-      <c r="B179" t="s">
-        <v>724</v>
-      </c>
       <c r="D179" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E179" t="s">
         <v>53</v>
       </c>
       <c r="F179" t="s">
+        <v>731</v>
+      </c>
+      <c r="J179" t="s">
         <v>732</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>733</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" s="1" t="s">
         <v>734</v>
-      </c>
-      <c r="L179" s="1" t="s">
-        <v>735</v>
       </c>
       <c r="R179" t="s">
         <v>61</v>
       </c>
       <c r="S179" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="W179">
         <v>3</v>
@@ -10738,28 +10735,28 @@
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>722</v>
+      </c>
+      <c r="B180" t="s">
         <v>723</v>
       </c>
-      <c r="B180" t="s">
-        <v>724</v>
-      </c>
       <c r="D180" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E180" t="s">
         <v>405</v>
       </c>
       <c r="F180" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J180" t="s">
+        <v>737</v>
+      </c>
+      <c r="K180" t="s">
         <v>738</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" s="1" t="s">
         <v>739</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>740</v>
       </c>
       <c r="R180" t="s">
         <v>30</v>
@@ -10779,13 +10776,13 @@
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>722</v>
+      </c>
+      <c r="B181" t="s">
         <v>723</v>
       </c>
-      <c r="B181" t="s">
-        <v>724</v>
-      </c>
       <c r="D181" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E181" t="s">
         <v>88</v>
@@ -10794,13 +10791,13 @@
         <v>89</v>
       </c>
       <c r="J181" t="s">
+        <v>741</v>
+      </c>
+      <c r="K181" t="s">
         <v>742</v>
       </c>
-      <c r="K181" t="s">
+      <c r="L181" s="1" t="s">
         <v>743</v>
-      </c>
-      <c r="L181" s="1" t="s">
-        <v>744</v>
       </c>
       <c r="R181" t="s">
         <v>30</v>
@@ -10820,10 +10817,10 @@
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>744</v>
+      </c>
+      <c r="B182" t="s">
         <v>745</v>
-      </c>
-      <c r="B182" t="s">
-        <v>746</v>
       </c>
       <c r="D182" t="s">
         <v>431</v>
@@ -10832,10 +10829,10 @@
         <v>482</v>
       </c>
       <c r="J182" t="s">
+        <v>746</v>
+      </c>
+      <c r="L182" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="L182" s="1" t="s">
-        <v>748</v>
       </c>
       <c r="R182" t="s">
         <v>30</v>
@@ -10855,22 +10852,22 @@
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>744</v>
+      </c>
+      <c r="B183" t="s">
         <v>745</v>
       </c>
-      <c r="B183" t="s">
-        <v>746</v>
-      </c>
       <c r="D183" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F183" t="s">
         <v>482</v>
       </c>
       <c r="J183" t="s">
+        <v>749</v>
+      </c>
+      <c r="L183" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="L183" s="1" t="s">
-        <v>751</v>
       </c>
       <c r="R183" t="s">
         <v>30</v>
@@ -10890,25 +10887,25 @@
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>744</v>
+      </c>
+      <c r="B184" t="s">
         <v>745</v>
       </c>
-      <c r="B184" t="s">
-        <v>746</v>
-      </c>
       <c r="D184" t="s">
+        <v>751</v>
+      </c>
+      <c r="E184" t="s">
         <v>752</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>753</v>
       </c>
-      <c r="F184" t="s">
+      <c r="J184" t="s">
         <v>754</v>
       </c>
-      <c r="J184" t="s">
+      <c r="L184" s="1" t="s">
         <v>755</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>756</v>
       </c>
       <c r="R184" t="s">
         <v>30</v>
@@ -10928,10 +10925,10 @@
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>756</v>
+      </c>
+      <c r="B185" t="s">
         <v>757</v>
-      </c>
-      <c r="B185" t="s">
-        <v>758</v>
       </c>
       <c r="D185" t="s">
         <v>230</v>
@@ -10943,10 +10940,10 @@
         <v>89</v>
       </c>
       <c r="J185" t="s">
+        <v>758</v>
+      </c>
+      <c r="L185" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>760</v>
       </c>
       <c r="R185" t="s">
         <v>30</v>
@@ -10966,25 +10963,25 @@
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>756</v>
+      </c>
+      <c r="B186" t="s">
         <v>757</v>
-      </c>
-      <c r="B186" t="s">
-        <v>758</v>
       </c>
       <c r="D186" t="s">
         <v>595</v>
       </c>
       <c r="E186" t="s">
+        <v>760</v>
+      </c>
+      <c r="F186" t="s">
         <v>761</v>
       </c>
-      <c r="F186" t="s">
+      <c r="J186" t="s">
         <v>762</v>
       </c>
-      <c r="J186" t="s">
+      <c r="L186" s="1" t="s">
         <v>763</v>
-      </c>
-      <c r="L186" s="1" t="s">
-        <v>764</v>
       </c>
       <c r="R186" t="s">
         <v>30</v>
@@ -11004,13 +11001,13 @@
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>756</v>
+      </c>
+      <c r="B187" t="s">
         <v>757</v>
       </c>
-      <c r="B187" t="s">
-        <v>758</v>
-      </c>
       <c r="D187" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E187" t="s">
         <v>88</v>
@@ -11019,13 +11016,13 @@
         <v>89</v>
       </c>
       <c r="J187" t="s">
+        <v>765</v>
+      </c>
+      <c r="K187" t="s">
         <v>766</v>
       </c>
-      <c r="K187" t="s">
+      <c r="L187" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="L187" s="1" t="s">
-        <v>768</v>
       </c>
       <c r="R187" t="s">
         <v>30</v>
@@ -11045,10 +11042,10 @@
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>756</v>
+      </c>
+      <c r="B188" t="s">
         <v>757</v>
-      </c>
-      <c r="B188" t="s">
-        <v>758</v>
       </c>
       <c r="D188" t="s">
         <v>496</v>
@@ -11063,10 +11060,10 @@
         <v>551</v>
       </c>
       <c r="K188" t="s">
+        <v>768</v>
+      </c>
+      <c r="L188" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>770</v>
       </c>
       <c r="R188" t="s">
         <v>30</v>
@@ -11086,40 +11083,40 @@
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>770</v>
+      </c>
+      <c r="B189" t="s">
         <v>771</v>
       </c>
-      <c r="B189" t="s">
+      <c r="D189" t="s">
         <v>772</v>
-      </c>
-      <c r="D189" t="s">
-        <v>773</v>
       </c>
       <c r="E189" t="s">
         <v>457</v>
       </c>
       <c r="F189" t="s">
+        <v>773</v>
+      </c>
+      <c r="J189" t="s">
         <v>774</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
         <v>775</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="L189" s="1" t="s">
+      <c r="M189" t="s">
         <v>777</v>
       </c>
-      <c r="M189" t="s">
+      <c r="N189" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="N189" s="1" t="s">
+      <c r="R189" t="s">
+        <v>30</v>
+      </c>
+      <c r="S189" t="s">
         <v>779</v>
-      </c>
-      <c r="R189" t="s">
-        <v>30</v>
-      </c>
-      <c r="S189" t="s">
-        <v>780</v>
       </c>
       <c r="T189">
         <v>460</v>
@@ -11133,34 +11130,34 @@
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>770</v>
+      </c>
+      <c r="B190" t="s">
         <v>771</v>
       </c>
-      <c r="B190" t="s">
-        <v>772</v>
-      </c>
       <c r="D190" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E190" t="s">
         <v>457</v>
       </c>
       <c r="F190" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="J190" t="s">
+        <v>781</v>
+      </c>
+      <c r="K190" t="s">
         <v>782</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="L190" s="1" t="s">
+      <c r="M190" t="s">
+        <v>777</v>
+      </c>
+      <c r="N190" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="M190" t="s">
-        <v>778</v>
-      </c>
-      <c r="N190" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="R190" t="s">
         <v>30</v>
@@ -11180,10 +11177,10 @@
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>770</v>
+      </c>
+      <c r="B191" t="s">
         <v>771</v>
-      </c>
-      <c r="B191" t="s">
-        <v>772</v>
       </c>
       <c r="D191" t="s">
         <v>95</v>
@@ -11195,13 +11192,13 @@
         <v>121</v>
       </c>
       <c r="J191" t="s">
+        <v>785</v>
+      </c>
+      <c r="K191" t="s">
         <v>786</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" s="1" t="s">
         <v>787</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="R191" t="s">
         <v>30</v>
@@ -11221,13 +11218,13 @@
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>770</v>
+      </c>
+      <c r="B192" t="s">
         <v>771</v>
       </c>
-      <c r="B192" t="s">
-        <v>772</v>
-      </c>
       <c r="D192" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E192" t="s">
         <v>48</v>
@@ -11236,13 +11233,13 @@
         <v>121</v>
       </c>
       <c r="J192" t="s">
+        <v>789</v>
+      </c>
+      <c r="K192" t="s">
         <v>790</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>792</v>
       </c>
       <c r="R192" t="s">
         <v>30</v>
@@ -11262,10 +11259,10 @@
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>770</v>
+      </c>
+      <c r="B193" t="s">
         <v>771</v>
-      </c>
-      <c r="B193" t="s">
-        <v>772</v>
       </c>
       <c r="D193" t="s">
         <v>100</v>
@@ -11277,13 +11274,13 @@
         <v>121</v>
       </c>
       <c r="J193" t="s">
+        <v>792</v>
+      </c>
+      <c r="K193" t="s">
         <v>793</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>795</v>
       </c>
       <c r="R193" t="s">
         <v>30</v>
@@ -11303,10 +11300,10 @@
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>770</v>
+      </c>
+      <c r="B194" t="s">
         <v>771</v>
-      </c>
-      <c r="B194" t="s">
-        <v>772</v>
       </c>
       <c r="D194" t="s">
         <v>412</v>
@@ -11318,13 +11315,13 @@
         <v>42</v>
       </c>
       <c r="J194" t="s">
+        <v>795</v>
+      </c>
+      <c r="K194" t="s">
         <v>796</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" s="1" t="s">
         <v>797</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>798</v>
       </c>
       <c r="R194" t="s">
         <v>30</v>
@@ -11344,13 +11341,13 @@
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>770</v>
+      </c>
+      <c r="B195" t="s">
         <v>771</v>
       </c>
-      <c r="B195" t="s">
-        <v>772</v>
-      </c>
       <c r="D195" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E195" t="s">
         <v>41</v>
@@ -11359,13 +11356,13 @@
         <v>42</v>
       </c>
       <c r="J195" t="s">
+        <v>799</v>
+      </c>
+      <c r="K195" t="s">
         <v>800</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" s="1" t="s">
         <v>801</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>802</v>
       </c>
       <c r="R195" t="s">
         <v>30</v>
@@ -11385,13 +11382,13 @@
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>770</v>
+      </c>
+      <c r="B196" t="s">
         <v>771</v>
       </c>
-      <c r="B196" t="s">
-        <v>772</v>
-      </c>
       <c r="D196" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E196" t="s">
         <v>88</v>
@@ -11400,13 +11397,13 @@
         <v>89</v>
       </c>
       <c r="J196" t="s">
+        <v>803</v>
+      </c>
+      <c r="K196" t="s">
         <v>804</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" s="1" t="s">
         <v>805</v>
-      </c>
-      <c r="L196" s="1" t="s">
-        <v>806</v>
       </c>
       <c r="R196" t="s">
         <v>30</v>
@@ -11426,28 +11423,28 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>770</v>
+      </c>
+      <c r="B197" t="s">
         <v>771</v>
-      </c>
-      <c r="B197" t="s">
-        <v>772</v>
       </c>
       <c r="D197" t="s">
         <v>57</v>
       </c>
       <c r="E197" t="s">
+        <v>639</v>
+      </c>
+      <c r="F197" t="s">
         <v>640</v>
       </c>
-      <c r="F197" t="s">
-        <v>641</v>
-      </c>
       <c r="J197" t="s">
+        <v>806</v>
+      </c>
+      <c r="K197" t="s">
         <v>807</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" s="1" t="s">
         <v>808</v>
-      </c>
-      <c r="L197" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="R197" t="s">
         <v>30</v>
@@ -11467,28 +11464,28 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>770</v>
+      </c>
+      <c r="B198" t="s">
         <v>771</v>
       </c>
-      <c r="B198" t="s">
-        <v>772</v>
-      </c>
       <c r="D198" t="s">
+        <v>809</v>
+      </c>
+      <c r="E198" t="s">
         <v>810</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>811</v>
       </c>
-      <c r="F198" t="s">
+      <c r="J198" t="s">
+        <v>727</v>
+      </c>
+      <c r="K198" t="s">
         <v>812</v>
       </c>
-      <c r="J198" t="s">
-        <v>728</v>
-      </c>
-      <c r="K198" t="s">
+      <c r="L198" s="1" t="s">
         <v>813</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>814</v>
       </c>
       <c r="R198" t="s">
         <v>30</v>
@@ -11511,22 +11508,22 @@
         <v>410</v>
       </c>
       <c r="B199" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D199" t="s">
         <v>215</v>
       </c>
       <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
         <v>706</v>
       </c>
-      <c r="F199" t="s">
-        <v>707</v>
-      </c>
       <c r="J199" t="s">
+        <v>815</v>
+      </c>
+      <c r="L199" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="L199" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="R199" t="s">
         <v>30</v>
@@ -11549,22 +11546,22 @@
         <v>410</v>
       </c>
       <c r="B200" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D200" t="s">
+        <v>817</v>
+      </c>
+      <c r="E200" t="s">
+        <v>639</v>
+      </c>
+      <c r="F200" t="s">
+        <v>640</v>
+      </c>
+      <c r="J200" t="s">
         <v>818</v>
       </c>
-      <c r="E200" t="s">
-        <v>640</v>
-      </c>
-      <c r="F200" t="s">
-        <v>641</v>
-      </c>
-      <c r="J200" t="s">
+      <c r="L200" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="L200" s="1" t="s">
-        <v>820</v>
       </c>
       <c r="R200" t="s">
         <v>30</v>
@@ -11587,10 +11584,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D201" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E201" t="s">
         <v>48</v>
@@ -11599,10 +11596,10 @@
         <v>121</v>
       </c>
       <c r="J201" t="s">
+        <v>821</v>
+      </c>
+      <c r="L201" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="L201" s="1" t="s">
-        <v>823</v>
       </c>
       <c r="R201" t="s">
         <v>30</v>
@@ -11625,10 +11622,10 @@
         <v>410</v>
       </c>
       <c r="B202" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D202" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E202" t="s">
         <v>48</v>
@@ -11637,10 +11634,10 @@
         <v>121</v>
       </c>
       <c r="J202" t="s">
+        <v>824</v>
+      </c>
+      <c r="L202" s="1" t="s">
         <v>825</v>
-      </c>
-      <c r="L202" s="1" t="s">
-        <v>826</v>
       </c>
       <c r="R202" t="s">
         <v>30</v>
@@ -11663,7 +11660,7 @@
         <v>566</v>
       </c>
       <c r="B203" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D203" t="s">
         <v>472</v>
@@ -11675,10 +11672,10 @@
         <v>27</v>
       </c>
       <c r="J203" t="s">
+        <v>827</v>
+      </c>
+      <c r="L203" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="L203" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="R203" t="s">
         <v>30</v>
@@ -11701,10 +11698,10 @@
         <v>566</v>
       </c>
       <c r="B204" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D204" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E204" t="s">
         <v>26</v>
@@ -11713,10 +11710,10 @@
         <v>27</v>
       </c>
       <c r="J204" t="s">
+        <v>830</v>
+      </c>
+      <c r="L204" s="1" t="s">
         <v>831</v>
-      </c>
-      <c r="L204" s="1" t="s">
-        <v>832</v>
       </c>
       <c r="R204" t="s">
         <v>30</v>
@@ -11739,10 +11736,10 @@
         <v>566</v>
       </c>
       <c r="B205" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D205" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E205" t="s">
         <v>33</v>
@@ -11751,10 +11748,10 @@
         <v>34</v>
       </c>
       <c r="J205" t="s">
+        <v>833</v>
+      </c>
+      <c r="L205" s="1" t="s">
         <v>834</v>
-      </c>
-      <c r="L205" s="1" t="s">
-        <v>835</v>
       </c>
       <c r="R205" t="s">
         <v>30</v>
@@ -11777,7 +11774,7 @@
         <v>566</v>
       </c>
       <c r="B206" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D206" t="s">
         <v>585</v>
@@ -11789,10 +11786,10 @@
         <v>27</v>
       </c>
       <c r="J206" t="s">
+        <v>835</v>
+      </c>
+      <c r="L206" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="L206" s="1" t="s">
-        <v>837</v>
       </c>
       <c r="R206" t="s">
         <v>30</v>
@@ -11812,25 +11809,25 @@
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>837</v>
+      </c>
+      <c r="B207" t="s">
         <v>838</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207" t="s">
         <v>839</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>840</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>841</v>
       </c>
-      <c r="F207" t="s">
+      <c r="J207" t="s">
         <v>842</v>
       </c>
-      <c r="J207" t="s">
+      <c r="L207" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="L207" s="1" t="s">
-        <v>844</v>
       </c>
       <c r="R207" t="s">
         <v>30</v>
@@ -11850,25 +11847,25 @@
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>837</v>
+      </c>
+      <c r="B208" t="s">
         <v>838</v>
-      </c>
-      <c r="B208" t="s">
-        <v>839</v>
       </c>
       <c r="D208" t="s">
         <v>206</v>
       </c>
       <c r="E208" t="s">
+        <v>844</v>
+      </c>
+      <c r="F208" t="s">
         <v>845</v>
       </c>
-      <c r="F208" t="s">
+      <c r="J208" t="s">
         <v>846</v>
       </c>
-      <c r="J208" t="s">
+      <c r="L208" s="1" t="s">
         <v>847</v>
-      </c>
-      <c r="L208" s="1" t="s">
-        <v>848</v>
       </c>
       <c r="R208" t="s">
         <v>30</v>
@@ -11888,25 +11885,25 @@
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>837</v>
+      </c>
+      <c r="B209" t="s">
         <v>838</v>
-      </c>
-      <c r="B209" t="s">
-        <v>839</v>
       </c>
       <c r="D209" t="s">
         <v>168</v>
       </c>
       <c r="E209" t="s">
+        <v>848</v>
+      </c>
+      <c r="F209" t="s">
         <v>849</v>
       </c>
-      <c r="F209" t="s">
+      <c r="J209" t="s">
         <v>850</v>
       </c>
-      <c r="J209" t="s">
+      <c r="L209" s="1" t="s">
         <v>851</v>
-      </c>
-      <c r="L209" s="1" t="s">
-        <v>852</v>
       </c>
       <c r="R209" t="s">
         <v>30</v>
@@ -11926,25 +11923,25 @@
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>837</v>
+      </c>
+      <c r="B210" t="s">
         <v>838</v>
-      </c>
-      <c r="B210" t="s">
-        <v>839</v>
       </c>
       <c r="D210" t="s">
         <v>82</v>
       </c>
       <c r="E210" t="s">
+        <v>852</v>
+      </c>
+      <c r="F210" t="s">
         <v>853</v>
       </c>
-      <c r="F210" t="s">
+      <c r="J210" t="s">
         <v>854</v>
       </c>
-      <c r="J210" t="s">
+      <c r="L210" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>856</v>
       </c>
       <c r="R210" t="s">
         <v>30</v>
@@ -11964,13 +11961,13 @@
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>856</v>
+      </c>
+      <c r="B211" t="s">
         <v>857</v>
       </c>
-      <c r="B211" t="s">
-        <v>858</v>
-      </c>
       <c r="D211" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E211" t="s">
         <v>88</v>
@@ -11979,10 +11976,10 @@
         <v>89</v>
       </c>
       <c r="J211" t="s">
+        <v>858</v>
+      </c>
+      <c r="L211" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="L211" s="1" t="s">
-        <v>860</v>
       </c>
       <c r="R211" t="s">
         <v>30</v>
@@ -12002,10 +11999,10 @@
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>856</v>
+      </c>
+      <c r="B212" t="s">
         <v>857</v>
-      </c>
-      <c r="B212" t="s">
-        <v>858</v>
       </c>
       <c r="D212" t="s">
         <v>87</v>
@@ -12017,10 +12014,10 @@
         <v>89</v>
       </c>
       <c r="J212" t="s">
+        <v>860</v>
+      </c>
+      <c r="L212" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="L212" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="R212" t="s">
         <v>30</v>
@@ -12040,13 +12037,13 @@
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>856</v>
+      </c>
+      <c r="B213" t="s">
         <v>857</v>
       </c>
-      <c r="B213" t="s">
-        <v>858</v>
-      </c>
       <c r="D213" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E213" t="s">
         <v>48</v>
@@ -12055,10 +12052,10 @@
         <v>121</v>
       </c>
       <c r="J213" t="s">
+        <v>863</v>
+      </c>
+      <c r="L213" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="L213" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="R213" t="s">
         <v>30</v>
@@ -12078,10 +12075,10 @@
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>856</v>
+      </c>
+      <c r="B214" t="s">
         <v>857</v>
-      </c>
-      <c r="B214" t="s">
-        <v>858</v>
       </c>
       <c r="D214" t="s">
         <v>230</v>
@@ -12093,10 +12090,10 @@
         <v>194</v>
       </c>
       <c r="J214" t="s">
+        <v>865</v>
+      </c>
+      <c r="L214" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="L214" s="1" t="s">
-        <v>867</v>
       </c>
       <c r="R214" t="s">
         <v>30</v>
@@ -12119,7 +12116,7 @@
         <v>177</v>
       </c>
       <c r="B215" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D215" t="s">
         <v>585</v>
@@ -12131,10 +12128,10 @@
         <v>416</v>
       </c>
       <c r="J215" t="s">
+        <v>868</v>
+      </c>
+      <c r="L215" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="L215" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="R215" t="s">
         <v>30</v>
@@ -12157,7 +12154,7 @@
         <v>177</v>
       </c>
       <c r="B216" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D216" t="s">
         <v>472</v>
@@ -12169,10 +12166,10 @@
         <v>42</v>
       </c>
       <c r="J216" t="s">
+        <v>870</v>
+      </c>
+      <c r="L216" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="L216" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="R216" t="s">
         <v>30</v>
@@ -12195,7 +12192,7 @@
         <v>177</v>
       </c>
       <c r="B217" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D217" t="s">
         <v>427</v>
@@ -12207,10 +12204,10 @@
         <v>27</v>
       </c>
       <c r="J217" t="s">
+        <v>872</v>
+      </c>
+      <c r="L217" s="1" t="s">
         <v>873</v>
-      </c>
-      <c r="L217" s="1" t="s">
-        <v>874</v>
       </c>
       <c r="R217" t="s">
         <v>30</v>
@@ -12233,7 +12230,7 @@
         <v>177</v>
       </c>
       <c r="B218" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D218" t="s">
         <v>326</v>
@@ -12245,10 +12242,10 @@
         <v>102</v>
       </c>
       <c r="J218" t="s">
+        <v>874</v>
+      </c>
+      <c r="L218" s="1" t="s">
         <v>875</v>
-      </c>
-      <c r="L218" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="R218" t="s">
         <v>30</v>
@@ -12268,13 +12265,13 @@
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>876</v>
+      </c>
+      <c r="B219" t="s">
         <v>877</v>
       </c>
-      <c r="B219" t="s">
+      <c r="D219" t="s">
         <v>878</v>
-      </c>
-      <c r="D219" t="s">
-        <v>879</v>
       </c>
       <c r="E219" t="s">
         <v>41</v>
@@ -12283,10 +12280,10 @@
         <v>529</v>
       </c>
       <c r="J219" t="s">
+        <v>879</v>
+      </c>
+      <c r="L219" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="L219" s="1" t="s">
-        <v>881</v>
       </c>
       <c r="R219" t="s">
         <v>30</v>
@@ -12306,10 +12303,10 @@
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>876</v>
+      </c>
+      <c r="B220" t="s">
         <v>877</v>
-      </c>
-      <c r="B220" t="s">
-        <v>878</v>
       </c>
       <c r="D220" t="s">
         <v>179</v>
@@ -12321,10 +12318,10 @@
         <v>89</v>
       </c>
       <c r="J220" t="s">
+        <v>881</v>
+      </c>
+      <c r="L220" s="1" t="s">
         <v>882</v>
-      </c>
-      <c r="L220" s="1" t="s">
-        <v>883</v>
       </c>
       <c r="R220" t="s">
         <v>30</v>
@@ -12344,13 +12341,13 @@
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>876</v>
+      </c>
+      <c r="B221" t="s">
         <v>877</v>
       </c>
-      <c r="B221" t="s">
-        <v>878</v>
-      </c>
       <c r="D221" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E221" t="s">
         <v>41</v>
@@ -12359,10 +12356,10 @@
         <v>42</v>
       </c>
       <c r="J221" t="s">
+        <v>883</v>
+      </c>
+      <c r="L221" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="L221" s="1" t="s">
-        <v>885</v>
       </c>
       <c r="R221" t="s">
         <v>30</v>
@@ -12382,10 +12379,10 @@
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>876</v>
+      </c>
+      <c r="B222" t="s">
         <v>877</v>
-      </c>
-      <c r="B222" t="s">
-        <v>878</v>
       </c>
       <c r="D222" t="s">
         <v>82</v>
@@ -12397,10 +12394,10 @@
         <v>371</v>
       </c>
       <c r="J222" t="s">
+        <v>885</v>
+      </c>
+      <c r="L222" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="L222" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="R222" t="s">
         <v>30</v>
@@ -12420,13 +12417,13 @@
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>876</v>
+      </c>
+      <c r="B223" t="s">
         <v>877</v>
       </c>
-      <c r="B223" t="s">
-        <v>878</v>
-      </c>
       <c r="D223" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E223" t="s">
         <v>41</v>
@@ -12435,10 +12432,10 @@
         <v>42</v>
       </c>
       <c r="J223" t="s">
+        <v>888</v>
+      </c>
+      <c r="L223" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="L223" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="R223" t="s">
         <v>30</v>
@@ -12458,25 +12455,25 @@
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>876</v>
+      </c>
+      <c r="B224" t="s">
         <v>877</v>
       </c>
-      <c r="B224" t="s">
-        <v>878</v>
-      </c>
       <c r="D224" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E224" t="s">
+        <v>890</v>
+      </c>
+      <c r="F224" t="s">
         <v>891</v>
       </c>
-      <c r="F224" t="s">
+      <c r="J224" t="s">
         <v>892</v>
       </c>
-      <c r="J224" t="s">
+      <c r="L224" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="L224" s="1" t="s">
-        <v>894</v>
       </c>
       <c r="R224" t="s">
         <v>30</v>
@@ -12496,25 +12493,25 @@
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>876</v>
+      </c>
+      <c r="B225" t="s">
         <v>877</v>
-      </c>
-      <c r="B225" t="s">
-        <v>878</v>
       </c>
       <c r="D225">
         <v>1624</v>
       </c>
       <c r="E225" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F225" t="s">
+        <v>894</v>
+      </c>
+      <c r="J225" t="s">
         <v>895</v>
       </c>
-      <c r="J225" t="s">
+      <c r="L225" s="1" t="s">
         <v>896</v>
-      </c>
-      <c r="L225" s="1" t="s">
-        <v>897</v>
       </c>
       <c r="R225" t="s">
         <v>30</v>
@@ -12534,10 +12531,10 @@
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>876</v>
+      </c>
+      <c r="B226" t="s">
         <v>877</v>
-      </c>
-      <c r="B226" t="s">
-        <v>878</v>
       </c>
       <c r="D226" t="s">
         <v>69</v>
@@ -12549,10 +12546,10 @@
         <v>246</v>
       </c>
       <c r="J226" t="s">
+        <v>897</v>
+      </c>
+      <c r="L226" s="1" t="s">
         <v>898</v>
-      </c>
-      <c r="L226" s="1" t="s">
-        <v>899</v>
       </c>
       <c r="R226" t="s">
         <v>30</v>
@@ -12575,22 +12572,22 @@
         <v>566</v>
       </c>
       <c r="B227" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D227" t="s">
         <v>100</v>
       </c>
       <c r="E227" t="s">
+        <v>639</v>
+      </c>
+      <c r="F227" t="s">
         <v>640</v>
       </c>
-      <c r="F227" t="s">
-        <v>641</v>
-      </c>
       <c r="J227" t="s">
+        <v>900</v>
+      </c>
+      <c r="L227" s="1" t="s">
         <v>901</v>
-      </c>
-      <c r="L227" s="1" t="s">
-        <v>902</v>
       </c>
       <c r="R227" t="s">
         <v>30</v>
@@ -12613,7 +12610,7 @@
         <v>566</v>
       </c>
       <c r="B228" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D228" t="s">
         <v>192</v>
@@ -12622,13 +12619,13 @@
         <v>33</v>
       </c>
       <c r="F228" t="s">
+        <v>902</v>
+      </c>
+      <c r="J228" t="s">
         <v>903</v>
       </c>
-      <c r="J228" t="s">
+      <c r="L228" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="L228" s="1" t="s">
-        <v>905</v>
       </c>
       <c r="R228" t="s">
         <v>30</v>
@@ -12651,19 +12648,19 @@
         <v>566</v>
       </c>
       <c r="B229" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D229" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F229" t="s">
+        <v>905</v>
+      </c>
+      <c r="J229" t="s">
         <v>906</v>
       </c>
-      <c r="J229" t="s">
+      <c r="L229" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="L229" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="R229" t="s">
         <v>30</v>
@@ -12686,7 +12683,7 @@
         <v>566</v>
       </c>
       <c r="B230" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D230" t="s">
         <v>496</v>
@@ -12698,10 +12695,10 @@
         <v>27</v>
       </c>
       <c r="J230" t="s">
+        <v>908</v>
+      </c>
+      <c r="L230" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="L230" s="1" t="s">
-        <v>910</v>
       </c>
       <c r="R230" t="s">
         <v>30</v>
@@ -12721,10 +12718,10 @@
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>910</v>
+      </c>
+      <c r="B231" t="s">
         <v>911</v>
-      </c>
-      <c r="B231" t="s">
-        <v>912</v>
       </c>
       <c r="D231" t="s">
         <v>47</v>
@@ -12736,10 +12733,10 @@
         <v>42</v>
       </c>
       <c r="J231" t="s">
+        <v>912</v>
+      </c>
+      <c r="L231" s="1" t="s">
         <v>913</v>
-      </c>
-      <c r="L231" s="1" t="s">
-        <v>914</v>
       </c>
       <c r="R231" t="s">
         <v>30</v>
@@ -12759,25 +12756,25 @@
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>910</v>
+      </c>
+      <c r="B232" t="s">
         <v>911</v>
-      </c>
-      <c r="B232" t="s">
-        <v>912</v>
       </c>
       <c r="D232" t="s">
         <v>412</v>
       </c>
       <c r="E232" t="s">
+        <v>914</v>
+      </c>
+      <c r="F232" t="s">
         <v>915</v>
       </c>
-      <c r="F232" t="s">
+      <c r="J232" t="s">
         <v>916</v>
       </c>
-      <c r="J232" t="s">
+      <c r="L232" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="L232" s="1" t="s">
-        <v>918</v>
       </c>
       <c r="R232" t="s">
         <v>30</v>
@@ -12797,10 +12794,10 @@
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>910</v>
+      </c>
+      <c r="B233" t="s">
         <v>911</v>
-      </c>
-      <c r="B233" t="s">
-        <v>912</v>
       </c>
       <c r="D233" t="s">
         <v>69</v>
@@ -12812,10 +12809,10 @@
         <v>89</v>
       </c>
       <c r="J233" t="s">
+        <v>918</v>
+      </c>
+      <c r="L233" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="L233" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="R233" t="s">
         <v>30</v>
@@ -12835,25 +12832,25 @@
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
+        <v>910</v>
+      </c>
+      <c r="B234" t="s">
         <v>911</v>
-      </c>
-      <c r="B234" t="s">
-        <v>912</v>
       </c>
       <c r="D234" t="s">
         <v>206</v>
       </c>
       <c r="E234" t="s">
+        <v>920</v>
+      </c>
+      <c r="F234" t="s">
         <v>921</v>
       </c>
-      <c r="F234" t="s">
+      <c r="J234" t="s">
         <v>922</v>
       </c>
-      <c r="J234" t="s">
+      <c r="L234" s="1" t="s">
         <v>923</v>
-      </c>
-      <c r="L234" s="1" t="s">
-        <v>924</v>
       </c>
       <c r="R234" t="s">
         <v>30</v>
@@ -12876,7 +12873,7 @@
         <v>93</v>
       </c>
       <c r="B235" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D235" t="s">
         <v>233</v>
@@ -12888,10 +12885,10 @@
         <v>27</v>
       </c>
       <c r="J235" t="s">
+        <v>925</v>
+      </c>
+      <c r="L235" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="L235" s="1" t="s">
-        <v>927</v>
       </c>
       <c r="R235" t="s">
         <v>30</v>
@@ -12914,7 +12911,7 @@
         <v>93</v>
       </c>
       <c r="B236" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D236" t="s">
         <v>256</v>
@@ -12926,10 +12923,10 @@
         <v>97</v>
       </c>
       <c r="J236" t="s">
+        <v>927</v>
+      </c>
+      <c r="L236" s="1" t="s">
         <v>928</v>
-      </c>
-      <c r="L236" s="1" t="s">
-        <v>929</v>
       </c>
       <c r="R236" t="s">
         <v>30</v>
@@ -12952,10 +12949,10 @@
         <v>93</v>
       </c>
       <c r="B237" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D237" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E237" t="s">
         <v>26</v>
@@ -12964,10 +12961,10 @@
         <v>27</v>
       </c>
       <c r="J237" t="s">
+        <v>930</v>
+      </c>
+      <c r="L237" s="1" t="s">
         <v>931</v>
-      </c>
-      <c r="L237" s="1" t="s">
-        <v>932</v>
       </c>
       <c r="R237" t="s">
         <v>30</v>
@@ -12990,7 +12987,7 @@
         <v>93</v>
       </c>
       <c r="B238" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D238" t="s">
         <v>461</v>
@@ -13002,10 +12999,10 @@
         <v>42</v>
       </c>
       <c r="J238" t="s">
+        <v>932</v>
+      </c>
+      <c r="L238" s="1" t="s">
         <v>933</v>
-      </c>
-      <c r="L238" s="1" t="s">
-        <v>934</v>
       </c>
       <c r="R238" t="s">
         <v>30</v>
@@ -13025,13 +13022,13 @@
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>934</v>
+      </c>
+      <c r="B239" t="s">
         <v>935</v>
       </c>
-      <c r="B239" t="s">
-        <v>936</v>
-      </c>
       <c r="D239" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E239" t="s">
         <v>33</v>
@@ -13040,13 +13037,13 @@
         <v>34</v>
       </c>
       <c r="J239" t="s">
+        <v>936</v>
+      </c>
+      <c r="K239" t="s">
         <v>937</v>
       </c>
-      <c r="K239" t="s">
+      <c r="L239" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="L239" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="R239" t="s">
         <v>30</v>
@@ -13066,13 +13063,13 @@
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>934</v>
+      </c>
+      <c r="B240" t="s">
         <v>935</v>
       </c>
-      <c r="B240" t="s">
-        <v>936</v>
-      </c>
       <c r="D240" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E240" t="s">
         <v>88</v>
@@ -13081,10 +13078,10 @@
         <v>89</v>
       </c>
       <c r="J240" t="s">
+        <v>939</v>
+      </c>
+      <c r="L240" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="L240" s="1" t="s">
-        <v>941</v>
       </c>
       <c r="R240" t="s">
         <v>30</v>
@@ -13104,25 +13101,25 @@
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>934</v>
+      </c>
+      <c r="B241" t="s">
         <v>935</v>
       </c>
-      <c r="B241" t="s">
-        <v>936</v>
-      </c>
       <c r="D241" t="s">
+        <v>941</v>
+      </c>
+      <c r="E241" t="s">
+        <v>705</v>
+      </c>
+      <c r="F241" t="s">
+        <v>706</v>
+      </c>
+      <c r="J241" t="s">
         <v>942</v>
       </c>
-      <c r="E241" t="s">
-        <v>706</v>
-      </c>
-      <c r="F241" t="s">
-        <v>707</v>
-      </c>
-      <c r="J241" t="s">
+      <c r="L241" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="L241" s="1" t="s">
-        <v>944</v>
       </c>
       <c r="R241" t="s">
         <v>30</v>
@@ -13142,10 +13139,10 @@
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>934</v>
+      </c>
+      <c r="B242" t="s">
         <v>935</v>
-      </c>
-      <c r="B242" t="s">
-        <v>936</v>
       </c>
       <c r="D242" t="s">
         <v>272</v>
@@ -13157,13 +13154,13 @@
         <v>27</v>
       </c>
       <c r="J242" t="s">
+        <v>944</v>
+      </c>
+      <c r="K242" t="s">
         <v>945</v>
       </c>
-      <c r="K242" t="s">
+      <c r="L242" s="1" t="s">
         <v>946</v>
-      </c>
-      <c r="L242" s="1" t="s">
-        <v>947</v>
       </c>
       <c r="R242" t="s">
         <v>30</v>
@@ -13183,25 +13180,25 @@
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>934</v>
+      </c>
+      <c r="B243" t="s">
         <v>935</v>
       </c>
-      <c r="B243" t="s">
-        <v>936</v>
-      </c>
       <c r="D243" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E243" t="s">
         <v>41</v>
       </c>
       <c r="F243" t="s">
+        <v>948</v>
+      </c>
+      <c r="J243" t="s">
         <v>949</v>
       </c>
-      <c r="J243" t="s">
+      <c r="L243" s="1" t="s">
         <v>950</v>
-      </c>
-      <c r="L243" s="1" t="s">
-        <v>951</v>
       </c>
       <c r="R243" t="s">
         <v>30</v>
@@ -13221,10 +13218,10 @@
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>934</v>
+      </c>
+      <c r="B244" t="s">
         <v>935</v>
-      </c>
-      <c r="B244" t="s">
-        <v>936</v>
       </c>
       <c r="D244" t="s">
         <v>326</v>
@@ -13236,10 +13233,10 @@
         <v>27</v>
       </c>
       <c r="J244" t="s">
+        <v>951</v>
+      </c>
+      <c r="L244" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="L244" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="R244" t="s">
         <v>30</v>
@@ -13259,13 +13256,13 @@
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>934</v>
+      </c>
+      <c r="B245" t="s">
         <v>935</v>
       </c>
-      <c r="B245" t="s">
-        <v>936</v>
-      </c>
       <c r="D245" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E245" t="s">
         <v>26</v>
@@ -13274,13 +13271,13 @@
         <v>27</v>
       </c>
       <c r="J245" t="s">
+        <v>953</v>
+      </c>
+      <c r="K245" t="s">
         <v>954</v>
       </c>
-      <c r="K245" t="s">
+      <c r="L245" s="1" t="s">
         <v>955</v>
-      </c>
-      <c r="L245" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="R245" t="s">
         <v>30</v>
@@ -13300,28 +13297,28 @@
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>934</v>
+      </c>
+      <c r="B246" t="s">
         <v>935</v>
       </c>
-      <c r="B246" t="s">
-        <v>936</v>
-      </c>
       <c r="D246" t="s">
+        <v>956</v>
+      </c>
+      <c r="E246" t="s">
+        <v>705</v>
+      </c>
+      <c r="F246" t="s">
+        <v>706</v>
+      </c>
+      <c r="J246" t="s">
         <v>957</v>
       </c>
-      <c r="E246" t="s">
-        <v>706</v>
-      </c>
-      <c r="F246" t="s">
-        <v>707</v>
-      </c>
-      <c r="J246" t="s">
+      <c r="K246" t="s">
         <v>958</v>
       </c>
-      <c r="K246" t="s">
+      <c r="L246" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="L246" s="1" t="s">
-        <v>960</v>
       </c>
       <c r="R246" t="s">
         <v>30</v>
@@ -13341,10 +13338,10 @@
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>934</v>
+      </c>
+      <c r="B247" t="s">
         <v>935</v>
-      </c>
-      <c r="B247" t="s">
-        <v>936</v>
       </c>
       <c r="D247" t="s">
         <v>336</v>
@@ -13356,13 +13353,13 @@
         <v>89</v>
       </c>
       <c r="J247" t="s">
+        <v>960</v>
+      </c>
+      <c r="K247" t="s">
         <v>961</v>
       </c>
-      <c r="K247" t="s">
+      <c r="L247" s="1" t="s">
         <v>962</v>
-      </c>
-      <c r="L247" s="1" t="s">
-        <v>963</v>
       </c>
       <c r="R247" t="s">
         <v>30</v>
@@ -13382,10 +13379,10 @@
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>934</v>
+      </c>
+      <c r="B248" t="s">
         <v>935</v>
-      </c>
-      <c r="B248" t="s">
-        <v>936</v>
       </c>
       <c r="D248" t="s">
         <v>461</v>
@@ -13397,13 +13394,13 @@
         <v>102</v>
       </c>
       <c r="J248" t="s">
+        <v>963</v>
+      </c>
+      <c r="K248" t="s">
         <v>964</v>
       </c>
-      <c r="K248" t="s">
+      <c r="L248" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="L248" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="R248" t="s">
         <v>30</v>
@@ -13423,28 +13420,28 @@
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>934</v>
+      </c>
+      <c r="B249" t="s">
         <v>935</v>
-      </c>
-      <c r="B249" t="s">
-        <v>936</v>
       </c>
       <c r="D249" t="s">
         <v>75</v>
       </c>
       <c r="E249" t="s">
+        <v>966</v>
+      </c>
+      <c r="F249" t="s">
         <v>967</v>
       </c>
-      <c r="F249" t="s">
+      <c r="J249" t="s">
         <v>968</v>
       </c>
-      <c r="J249" t="s">
+      <c r="K249" t="s">
         <v>969</v>
       </c>
-      <c r="K249" t="s">
+      <c r="L249" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="L249" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="R249" t="s">
         <v>30</v>
@@ -13464,28 +13461,28 @@
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
+        <v>934</v>
+      </c>
+      <c r="B250" t="s">
         <v>935</v>
       </c>
-      <c r="B250" t="s">
-        <v>936</v>
-      </c>
       <c r="D250" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E250" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F250" t="s">
+        <v>971</v>
+      </c>
+      <c r="J250" t="s">
         <v>972</v>
       </c>
-      <c r="J250" t="s">
+      <c r="K250" t="s">
         <v>973</v>
       </c>
-      <c r="K250" t="s">
+      <c r="L250" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="L250" s="1" t="s">
-        <v>975</v>
       </c>
       <c r="R250" t="s">
         <v>30</v>
@@ -13505,10 +13502,10 @@
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>934</v>
+      </c>
+      <c r="B251" t="s">
         <v>935</v>
-      </c>
-      <c r="B251" t="s">
-        <v>936</v>
       </c>
       <c r="D251" t="s">
         <v>595</v>
@@ -13520,13 +13517,13 @@
         <v>27</v>
       </c>
       <c r="J251" t="s">
+        <v>975</v>
+      </c>
+      <c r="K251" t="s">
         <v>976</v>
       </c>
-      <c r="K251" t="s">
+      <c r="L251" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="L251" s="1" t="s">
-        <v>978</v>
       </c>
       <c r="R251" t="s">
         <v>30</v>
@@ -13546,13 +13543,13 @@
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>934</v>
+      </c>
+      <c r="B252" t="s">
         <v>935</v>
       </c>
-      <c r="B252" t="s">
-        <v>936</v>
-      </c>
       <c r="D252" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E252" t="s">
         <v>245</v>
@@ -13561,13 +13558,13 @@
         <v>246</v>
       </c>
       <c r="J252" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="K252" t="s">
         <v>552</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="R252" t="s">
         <v>30</v>
@@ -13587,10 +13584,10 @@
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>934</v>
+      </c>
+      <c r="B253" t="s">
         <v>935</v>
-      </c>
-      <c r="B253" t="s">
-        <v>936</v>
       </c>
       <c r="D253">
         <v>1627</v>
@@ -13602,10 +13599,10 @@
         <v>194</v>
       </c>
       <c r="J253" t="s">
+        <v>981</v>
+      </c>
+      <c r="L253" s="1" t="s">
         <v>982</v>
-      </c>
-      <c r="L253" s="1" t="s">
-        <v>983</v>
       </c>
       <c r="R253" t="s">
         <v>30</v>
@@ -13628,7 +13625,7 @@
         <v>444</v>
       </c>
       <c r="B254" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D254" t="s">
         <v>585</v>
@@ -13640,10 +13637,10 @@
         <v>97</v>
       </c>
       <c r="J254" t="s">
+        <v>984</v>
+      </c>
+      <c r="L254" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="L254" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="R254" t="s">
         <v>30</v>
@@ -13666,7 +13663,7 @@
         <v>444</v>
       </c>
       <c r="B255" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D255" t="s">
         <v>427</v>
@@ -13678,10 +13675,10 @@
         <v>27</v>
       </c>
       <c r="J255" t="s">
+        <v>986</v>
+      </c>
+      <c r="L255" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="L255" s="1" t="s">
-        <v>988</v>
       </c>
       <c r="R255" t="s">
         <v>30</v>
@@ -13704,10 +13701,10 @@
         <v>444</v>
       </c>
       <c r="B256" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D256" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E256" t="s">
         <v>33</v>
@@ -13716,10 +13713,10 @@
         <v>34</v>
       </c>
       <c r="J256" t="s">
+        <v>988</v>
+      </c>
+      <c r="L256" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="L256" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="R256" t="s">
         <v>30</v>
@@ -13742,7 +13739,7 @@
         <v>444</v>
       </c>
       <c r="B257" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D257" t="s">
         <v>427</v>
@@ -13754,10 +13751,10 @@
         <v>102</v>
       </c>
       <c r="J257" t="s">
+        <v>990</v>
+      </c>
+      <c r="L257" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="L257" s="1" t="s">
-        <v>992</v>
       </c>
       <c r="R257" t="s">
         <v>30</v>
@@ -13777,10 +13774,10 @@
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>992</v>
+      </c>
+      <c r="B258" t="s">
         <v>993</v>
-      </c>
-      <c r="B258" t="s">
-        <v>994</v>
       </c>
       <c r="D258" t="s">
         <v>244</v>
@@ -13792,10 +13789,10 @@
         <v>27</v>
       </c>
       <c r="J258" t="s">
+        <v>994</v>
+      </c>
+      <c r="L258" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="L258" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="R258" t="s">
         <v>30</v>
@@ -13815,10 +13812,10 @@
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>992</v>
+      </c>
+      <c r="B259" t="s">
         <v>993</v>
-      </c>
-      <c r="B259" t="s">
-        <v>994</v>
       </c>
       <c r="D259" t="s">
         <v>192</v>
@@ -13830,10 +13827,10 @@
         <v>89</v>
       </c>
       <c r="J259" t="s">
+        <v>996</v>
+      </c>
+      <c r="L259" s="1" t="s">
         <v>997</v>
-      </c>
-      <c r="L259" s="1" t="s">
-        <v>998</v>
       </c>
       <c r="R259" t="s">
         <v>30</v>
@@ -13853,13 +13850,13 @@
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>992</v>
+      </c>
+      <c r="B260" t="s">
         <v>993</v>
       </c>
-      <c r="B260" t="s">
-        <v>994</v>
-      </c>
       <c r="D260" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E260" t="s">
         <v>33</v>
@@ -13868,10 +13865,10 @@
         <v>34</v>
       </c>
       <c r="J260" t="s">
+        <v>998</v>
+      </c>
+      <c r="L260" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="L260" s="1" t="s">
-        <v>1000</v>
       </c>
       <c r="R260" t="s">
         <v>30</v>
@@ -13891,10 +13888,10 @@
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>992</v>
+      </c>
+      <c r="B261" t="s">
         <v>993</v>
-      </c>
-      <c r="B261" t="s">
-        <v>994</v>
       </c>
       <c r="D261" t="s">
         <v>87</v>
@@ -13906,10 +13903,10 @@
         <v>27</v>
       </c>
       <c r="J261" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L261" s="1" t="s">
         <v>1001</v>
-      </c>
-      <c r="L261" s="1" t="s">
-        <v>1002</v>
       </c>
       <c r="R261" t="s">
         <v>30</v>
@@ -13929,13 +13926,13 @@
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B262" t="s">
         <v>1003</v>
       </c>
-      <c r="B262" t="s">
-        <v>1004</v>
-      </c>
       <c r="D262" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E262" t="s">
         <v>48</v>
@@ -13944,13 +13941,13 @@
         <v>121</v>
       </c>
       <c r="J262" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K262" t="s">
         <v>1005</v>
       </c>
-      <c r="K262" t="s">
+      <c r="L262" s="1" t="s">
         <v>1006</v>
-      </c>
-      <c r="L262" s="1" t="s">
-        <v>1007</v>
       </c>
       <c r="R262" t="s">
         <v>30</v>
@@ -13970,13 +13967,13 @@
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B263" t="s">
         <v>1003</v>
       </c>
-      <c r="B263" t="s">
-        <v>1004</v>
-      </c>
       <c r="D263" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E263" t="s">
         <v>41</v>
@@ -13985,13 +13982,13 @@
         <v>42</v>
       </c>
       <c r="J263" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K263" t="s">
         <v>1009</v>
       </c>
-      <c r="K263" t="s">
+      <c r="L263" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="L263" s="1" t="s">
-        <v>1011</v>
       </c>
       <c r="R263" t="s">
         <v>30</v>
@@ -14011,10 +14008,10 @@
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B264" t="s">
         <v>1003</v>
-      </c>
-      <c r="B264" t="s">
-        <v>1004</v>
       </c>
       <c r="D264" t="s">
         <v>192</v>
@@ -14026,13 +14023,13 @@
         <v>147</v>
       </c>
       <c r="J264" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K264" t="s">
         <v>1012</v>
       </c>
-      <c r="K264" t="s">
+      <c r="L264" s="1" t="s">
         <v>1013</v>
-      </c>
-      <c r="L264" s="1" t="s">
-        <v>1014</v>
       </c>
       <c r="R264" t="s">
         <v>30</v>
@@ -14052,10 +14049,10 @@
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B265" t="s">
         <v>1003</v>
-      </c>
-      <c r="B265" t="s">
-        <v>1004</v>
       </c>
       <c r="D265" t="s">
         <v>595</v>
@@ -14067,13 +14064,13 @@
         <v>121</v>
       </c>
       <c r="J265" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K265" t="s">
         <v>1015</v>
       </c>
-      <c r="K265" t="s">
+      <c r="L265" s="1" t="s">
         <v>1016</v>
-      </c>
-      <c r="L265" s="1" t="s">
-        <v>1017</v>
       </c>
       <c r="R265" t="s">
         <v>30</v>
@@ -14093,13 +14090,13 @@
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B266" t="s">
         <v>1003</v>
       </c>
-      <c r="B266" t="s">
-        <v>1004</v>
-      </c>
       <c r="D266" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E266" t="s">
         <v>41</v>
@@ -14108,13 +14105,13 @@
         <v>42</v>
       </c>
       <c r="J266" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K266" t="s">
         <v>1019</v>
       </c>
-      <c r="K266" t="s">
+      <c r="L266" s="1" t="s">
         <v>1020</v>
-      </c>
-      <c r="L266" s="1" t="s">
-        <v>1021</v>
       </c>
       <c r="R266" t="s">
         <v>30</v>
@@ -14134,13 +14131,13 @@
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B267" t="s">
         <v>1003</v>
       </c>
-      <c r="B267" t="s">
-        <v>1004</v>
-      </c>
       <c r="D267" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E267" t="s">
         <v>48</v>
@@ -14149,13 +14146,13 @@
         <v>121</v>
       </c>
       <c r="J267" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K267" t="s">
         <v>1023</v>
       </c>
-      <c r="K267" t="s">
+      <c r="L267" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="L267" s="1" t="s">
-        <v>1025</v>
       </c>
       <c r="R267" t="s">
         <v>30</v>
@@ -14175,10 +14172,10 @@
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B268" t="s">
         <v>1003</v>
-      </c>
-      <c r="B268" t="s">
-        <v>1004</v>
       </c>
       <c r="D268" t="s">
         <v>168</v>
@@ -14190,13 +14187,13 @@
         <v>121</v>
       </c>
       <c r="J268" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K268" t="s">
         <v>1026</v>
       </c>
-      <c r="K268" t="s">
+      <c r="L268" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="L268" s="1" t="s">
-        <v>1028</v>
       </c>
       <c r="R268" t="s">
         <v>30</v>
@@ -14216,10 +14213,10 @@
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B269" t="s">
         <v>1003</v>
-      </c>
-      <c r="B269" t="s">
-        <v>1004</v>
       </c>
       <c r="D269" t="s">
         <v>179</v>
@@ -14231,13 +14228,13 @@
         <v>121</v>
       </c>
       <c r="J269" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K269" t="s">
         <v>1029</v>
       </c>
-      <c r="K269" t="s">
+      <c r="L269" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="L269" s="1" t="s">
-        <v>1031</v>
       </c>
       <c r="R269" t="s">
         <v>30</v>
@@ -14257,10 +14254,10 @@
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B270" t="s">
         <v>1003</v>
-      </c>
-      <c r="B270" t="s">
-        <v>1004</v>
       </c>
       <c r="D270" t="s">
         <v>352</v>
@@ -14269,16 +14266,16 @@
         <v>101</v>
       </c>
       <c r="F270" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J270" t="s">
         <v>1032</v>
       </c>
-      <c r="J270" t="s">
+      <c r="K270" t="s">
         <v>1033</v>
       </c>
-      <c r="K270" t="s">
+      <c r="L270" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="L270" s="1" t="s">
-        <v>1035</v>
       </c>
       <c r="R270" t="s">
         <v>30</v>
@@ -14298,10 +14295,10 @@
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B271" t="s">
         <v>1003</v>
-      </c>
-      <c r="B271" t="s">
-        <v>1004</v>
       </c>
       <c r="D271" t="s">
         <v>192</v>
@@ -14313,13 +14310,13 @@
         <v>102</v>
       </c>
       <c r="J271" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K271" t="s">
         <v>1036</v>
       </c>
-      <c r="K271" t="s">
+      <c r="L271" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="L271" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="R271" t="s">
         <v>30</v>
@@ -14339,10 +14336,10 @@
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B272" t="s">
         <v>1003</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1004</v>
       </c>
       <c r="D272" t="s">
         <v>589</v>
@@ -14354,13 +14351,13 @@
         <v>121</v>
       </c>
       <c r="J272" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K272" t="s">
         <v>1039</v>
       </c>
-      <c r="K272" t="s">
+      <c r="L272" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="L272" s="1" t="s">
-        <v>1041</v>
       </c>
       <c r="R272" t="s">
         <v>30</v>
@@ -14380,13 +14377,13 @@
     </row>
     <row r="273" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B273" t="s">
         <v>1003</v>
       </c>
-      <c r="B273" t="s">
-        <v>1004</v>
-      </c>
       <c r="D273" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E273" t="s">
         <v>155</v>
@@ -14395,13 +14392,13 @@
         <v>156</v>
       </c>
       <c r="J273" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K273" t="s">
         <v>1042</v>
       </c>
-      <c r="K273" t="s">
+      <c r="L273" s="1" t="s">
         <v>1043</v>
-      </c>
-      <c r="L273" s="1" t="s">
-        <v>1044</v>
       </c>
       <c r="R273" t="s">
         <v>30</v>
@@ -14421,13 +14418,13 @@
     </row>
     <row r="274" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B274" t="s">
         <v>1045</v>
       </c>
-      <c r="B274" t="s">
+      <c r="D274" t="s">
         <v>1046</v>
-      </c>
-      <c r="D274" t="s">
-        <v>1047</v>
       </c>
       <c r="E274" t="s">
         <v>26</v>
@@ -14436,13 +14433,13 @@
         <v>27</v>
       </c>
       <c r="J274" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K274" t="s">
         <v>1048</v>
       </c>
-      <c r="K274" t="s">
+      <c r="L274" s="1" t="s">
         <v>1049</v>
-      </c>
-      <c r="L274" s="1" t="s">
-        <v>1050</v>
       </c>
       <c r="R274" t="s">
         <v>30</v>
@@ -14462,10 +14459,10 @@
     </row>
     <row r="275" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B275" t="s">
         <v>1045</v>
-      </c>
-      <c r="B275" t="s">
-        <v>1046</v>
       </c>
       <c r="D275" t="s">
         <v>481</v>
@@ -14483,7 +14480,7 @@
         <v>334</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="R275" t="s">
         <v>30</v>
@@ -14503,10 +14500,10 @@
     </row>
     <row r="276" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B276" t="s">
         <v>1045</v>
-      </c>
-      <c r="B276" t="s">
-        <v>1046</v>
       </c>
       <c r="D276" t="s">
         <v>326</v>
@@ -14518,13 +14515,13 @@
         <v>34</v>
       </c>
       <c r="J276" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K276" t="s">
         <v>1052</v>
       </c>
-      <c r="K276" t="s">
+      <c r="L276" s="1" t="s">
         <v>1053</v>
-      </c>
-      <c r="L276" s="1" t="s">
-        <v>1054</v>
       </c>
       <c r="R276" t="s">
         <v>30</v>
@@ -14544,13 +14541,13 @@
     </row>
     <row r="277" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B277" t="s">
         <v>1045</v>
       </c>
-      <c r="B277" t="s">
-        <v>1046</v>
-      </c>
       <c r="D277" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E277" t="s">
         <v>155</v>
@@ -14559,13 +14556,13 @@
         <v>156</v>
       </c>
       <c r="J277" t="s">
+        <v>1055</v>
+      </c>
+      <c r="K277" t="s">
         <v>1056</v>
       </c>
-      <c r="K277" t="s">
+      <c r="L277" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="L277" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="R277" t="s">
         <v>30</v>
@@ -14585,13 +14582,13 @@
     </row>
     <row r="278" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B278" t="s">
         <v>1045</v>
       </c>
-      <c r="B278" t="s">
-        <v>1046</v>
-      </c>
       <c r="D278" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E278" t="s">
         <v>88</v>
@@ -14600,13 +14597,13 @@
         <v>89</v>
       </c>
       <c r="J278" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K278" t="s">
         <v>1060</v>
       </c>
-      <c r="K278" t="s">
+      <c r="L278" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="L278" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="R278" t="s">
         <v>30</v>
@@ -14626,13 +14623,13 @@
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B279" t="s">
         <v>1045</v>
       </c>
-      <c r="B279" t="s">
-        <v>1046</v>
-      </c>
       <c r="D279" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E279" t="s">
         <v>88</v>
@@ -14641,13 +14638,13 @@
         <v>89</v>
       </c>
       <c r="J279" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K279" t="s">
         <v>1064</v>
       </c>
-      <c r="K279" t="s">
+      <c r="L279" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="L279" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="R279" t="s">
         <v>30</v>
@@ -14667,13 +14664,13 @@
     </row>
     <row r="280" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B280" t="s">
         <v>1045</v>
       </c>
-      <c r="B280" t="s">
-        <v>1046</v>
-      </c>
       <c r="D280" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E280" t="s">
         <v>106</v>
@@ -14682,13 +14679,13 @@
         <v>107</v>
       </c>
       <c r="J280" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K280" t="s">
         <v>1068</v>
       </c>
-      <c r="K280" t="s">
+      <c r="L280" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="L280" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="R280" t="s">
         <v>30</v>
@@ -14708,28 +14705,28 @@
     </row>
     <row r="281" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B281" t="s">
         <v>1045</v>
       </c>
-      <c r="B281" t="s">
-        <v>1046</v>
-      </c>
       <c r="D281" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E281" t="s">
         <v>96</v>
       </c>
       <c r="F281" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="J281" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K281" t="s">
         <v>1072</v>
       </c>
-      <c r="K281" t="s">
+      <c r="L281" s="1" t="s">
         <v>1073</v>
-      </c>
-      <c r="L281" s="1" t="s">
-        <v>1074</v>
       </c>
       <c r="R281" t="s">
         <v>30</v>
@@ -14749,13 +14746,13 @@
     </row>
     <row r="282" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B282" t="s">
         <v>1045</v>
       </c>
-      <c r="B282" t="s">
-        <v>1046</v>
-      </c>
       <c r="D282" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E282" t="s">
         <v>26</v>
@@ -14764,13 +14761,13 @@
         <v>27</v>
       </c>
       <c r="J282" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K282" t="s">
         <v>1076</v>
       </c>
-      <c r="K282" t="s">
+      <c r="L282" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="L282" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="R282" t="s">
         <v>30</v>
@@ -14790,28 +14787,28 @@
     </row>
     <row r="283" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B283" t="s">
         <v>1045</v>
       </c>
-      <c r="B283" t="s">
-        <v>1046</v>
-      </c>
       <c r="D283" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E283" t="s">
+        <v>630</v>
+      </c>
+      <c r="F283" t="s">
+        <v>631</v>
+      </c>
+      <c r="J283" t="s">
         <v>1079</v>
       </c>
-      <c r="E283" t="s">
-        <v>631</v>
-      </c>
-      <c r="F283" t="s">
-        <v>632</v>
-      </c>
-      <c r="J283" t="s">
+      <c r="K283" t="s">
         <v>1080</v>
       </c>
-      <c r="K283" t="s">
+      <c r="L283" s="1" t="s">
         <v>1081</v>
-      </c>
-      <c r="L283" s="1" t="s">
-        <v>1082</v>
       </c>
       <c r="R283" t="s">
         <v>30</v>
@@ -14831,13 +14828,13 @@
     </row>
     <row r="284" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B284" t="s">
         <v>1045</v>
       </c>
-      <c r="B284" t="s">
-        <v>1046</v>
-      </c>
       <c r="D284" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E284" t="s">
         <v>260</v>
@@ -14846,13 +14843,13 @@
         <v>97</v>
       </c>
       <c r="J284" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K284" t="s">
         <v>1084</v>
       </c>
-      <c r="K284" t="s">
+      <c r="L284" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="L284" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="R284" t="s">
         <v>30</v>
@@ -14872,13 +14869,13 @@
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B285" t="s">
         <v>1045</v>
       </c>
-      <c r="B285" t="s">
-        <v>1046</v>
-      </c>
       <c r="D285" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E285" t="s">
         <v>245</v>
@@ -14887,13 +14884,13 @@
         <v>246</v>
       </c>
       <c r="J285" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K285" t="s">
         <v>1088</v>
       </c>
-      <c r="K285" t="s">
+      <c r="L285" s="1" t="s">
         <v>1089</v>
-      </c>
-      <c r="L285" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="R285" t="s">
         <v>30</v>
@@ -14913,10 +14910,10 @@
     </row>
     <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B286" t="s">
         <v>1091</v>
-      </c>
-      <c r="B286" t="s">
-        <v>1092</v>
       </c>
       <c r="D286" t="s">
         <v>174</v>
@@ -14928,10 +14925,10 @@
         <v>121</v>
       </c>
       <c r="J286" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L286" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="L286" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="R286" t="s">
         <v>30</v>
@@ -14951,13 +14948,13 @@
     </row>
     <row r="287" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B287" t="s">
         <v>1091</v>
       </c>
-      <c r="B287" t="s">
-        <v>1092</v>
-      </c>
       <c r="D287" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E287" t="s">
         <v>260</v>
@@ -14966,10 +14963,10 @@
         <v>97</v>
       </c>
       <c r="J287" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L287" s="1" t="s">
         <v>1095</v>
-      </c>
-      <c r="L287" s="1" t="s">
-        <v>1096</v>
       </c>
       <c r="R287" t="s">
         <v>30</v>
@@ -14989,10 +14986,10 @@
     </row>
     <row r="288" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B288" t="s">
         <v>1091</v>
-      </c>
-      <c r="B288" t="s">
-        <v>1092</v>
       </c>
       <c r="D288" t="s">
         <v>95</v>
@@ -15004,10 +15001,10 @@
         <v>89</v>
       </c>
       <c r="J288" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L288" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="L288" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="R288" t="s">
         <v>30</v>
@@ -15027,10 +15024,10 @@
     </row>
     <row r="289" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B289" t="s">
         <v>1091</v>
-      </c>
-      <c r="B289" t="s">
-        <v>1092</v>
       </c>
       <c r="D289" t="s">
         <v>496</v>
@@ -15042,10 +15039,10 @@
         <v>89</v>
       </c>
       <c r="J289" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L289" s="1" t="s">
         <v>1099</v>
-      </c>
-      <c r="L289" s="1" t="s">
-        <v>1100</v>
       </c>
       <c r="R289" t="s">
         <v>30</v>
@@ -15065,13 +15062,13 @@
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B290" t="s">
         <v>1101</v>
       </c>
-      <c r="B290" t="s">
+      <c r="D290" t="s">
         <v>1102</v>
-      </c>
-      <c r="D290" t="s">
-        <v>1103</v>
       </c>
       <c r="E290" t="s">
         <v>53</v>
@@ -15080,10 +15077,10 @@
         <v>211</v>
       </c>
       <c r="J290" t="s">
+        <v>1103</v>
+      </c>
+      <c r="L290" s="1" t="s">
         <v>1104</v>
-      </c>
-      <c r="L290" s="1" t="s">
-        <v>1105</v>
       </c>
       <c r="R290" t="s">
         <v>30</v>
@@ -15103,13 +15100,13 @@
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B291" t="s">
         <v>1101</v>
       </c>
-      <c r="B291" t="s">
-        <v>1102</v>
-      </c>
       <c r="D291" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E291" t="s">
         <v>53</v>
@@ -15118,10 +15115,10 @@
         <v>70</v>
       </c>
       <c r="J291" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L291" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="L291" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="R291" t="s">
         <v>30</v>
@@ -15141,13 +15138,13 @@
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B292" t="s">
         <v>1101</v>
       </c>
-      <c r="B292" t="s">
-        <v>1102</v>
-      </c>
       <c r="D292" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E292" t="s">
         <v>53</v>
@@ -15156,10 +15153,10 @@
         <v>70</v>
       </c>
       <c r="J292" t="s">
+        <v>1108</v>
+      </c>
+      <c r="L292" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="L292" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="R292" t="s">
         <v>30</v>
@@ -15179,25 +15176,25 @@
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B293" t="s">
         <v>1101</v>
       </c>
-      <c r="B293" t="s">
-        <v>1102</v>
-      </c>
       <c r="D293" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E293" t="s">
+        <v>725</v>
+      </c>
+      <c r="F293" t="s">
+        <v>726</v>
+      </c>
+      <c r="J293" t="s">
         <v>1111</v>
       </c>
-      <c r="E293" t="s">
-        <v>726</v>
-      </c>
-      <c r="F293" t="s">
-        <v>727</v>
-      </c>
-      <c r="J293" t="s">
+      <c r="L293" s="1" t="s">
         <v>1112</v>
-      </c>
-      <c r="L293" s="1" t="s">
-        <v>1113</v>
       </c>
       <c r="R293" t="s">
         <v>30</v>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -9045,7 +9045,7 @@
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERISI </t>
+          <t>MERISI</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERISI </t>
+          <t>MERISI</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERISI </t>
+          <t>MERISI</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERISI </t>
+          <t>MERISI</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Conversion_on_the_Way_to_Damascus-Caravaggio_%28c.1600-1%29.jpg/960px-Conversion_on_the_Way_to_Damascus-Caravaggio_%28c.1600-1%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId150"/>
@@ -18179,7 +18179,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/F4522_Louvre_Rubens_debarquement_de_la_reine_a_Marseille_rwk.jpg/960px-F4522_Louvre_Rubens_debarquement_de_la_reine_a_Marseille_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId205"/>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E322F-7ABF-4E55-88B1-6AF3D49158C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35F5940-8EE4-46B3-9907-E0685D8D6DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="1208">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2341,7 +2341,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/22/Mattia_Preti_-_Baldassarre%27s_Feast_-_WGA18380.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>vers 1657</t>
+    <t>1657 environ</t>
   </si>
   <si>
     <t>Saint Sébastien</t>
@@ -2881,9 +2881,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ee/Anthony_van_Dyck_-_Self-portrait_with_a_Sunflower.jpg/1280px-Anthony_van_Dyck_-_Self-portrait_with_a_Sunflower.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Les Enfants de Charles Ier</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Anthony_van_Dyck_%281599-1641%29_-_The_Five_Eldest_Children_of_Charles_I_-_267_-_Royal_Collection.jpg/1280px-Anthony_van_Dyck_%281599-1641%29_-_The_Five_Eldest_Children_of_Charles_I_-_267_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -3641,6 +3638,12 @@
   </si>
   <si>
     <t>Adélaîde</t>
+  </si>
+  <si>
+    <t>Les Cinq Enfants de Charles Ier</t>
+  </si>
+  <si>
+    <t>1635-1636</t>
   </si>
 </sst>
 </file>
@@ -4804,7 +4807,7 @@
         <v>113</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="L18" s="17" t="s">
         <v>114</v>
@@ -4842,7 +4845,7 @@
         <v>117</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="L19" s="17" t="s">
         <v>118</v>
@@ -4874,16 +4877,16 @@
         <v>1615</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>1178</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>30</v>
@@ -4918,7 +4921,7 @@
         <v>121</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="L21" s="17" t="s">
         <v>122</v>
@@ -5111,7 +5114,7 @@
         <v>142</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>53</v>
@@ -5187,31 +5190,31 @@
         <v>53</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>653</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>1167</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="R28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="T28" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="T28" s="3" t="s">
+      <c r="U28" s="3" t="s">
         <v>1170</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>1171</v>
       </c>
       <c r="W28" s="3">
         <v>2</v>
@@ -5266,10 +5269,10 @@
         <v>156</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>1181</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>157</v>
@@ -5415,7 +5418,7 @@
         <v>165</v>
       </c>
       <c r="D34" s="2">
-        <v>1361</v>
+        <v>1631</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>91</v>
@@ -6035,7 +6038,7 @@
         <v>210</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>225</v>
@@ -6225,7 +6228,7 @@
         <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>245</v>
@@ -6265,8 +6268,15 @@
       <c r="D56" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>388</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Palais de Buckingham</t>
+        </is>
       </c>
       <c r="J56" s="2" t="s">
         <v>248</v>
@@ -6459,7 +6469,7 @@
         <v>265</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="L61" s="6" t="s">
         <v>266</v>
@@ -6488,7 +6498,7 @@
         <v>251</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>83</v>
@@ -6699,7 +6709,7 @@
         <v>283</v>
       </c>
       <c r="L67" s="17" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>30</v>
@@ -7155,7 +7165,7 @@
         <v>319</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>325</v>
@@ -7202,7 +7212,7 @@
         <v>27</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="L80" s="6" t="s">
         <v>330</v>
@@ -7351,7 +7361,7 @@
         <v>339</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>105</v>
@@ -7816,7 +7826,7 @@
         <v>1612</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>181</v>
@@ -8190,7 +8200,7 @@
         <v>426</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>245</v>
@@ -8430,7 +8440,7 @@
         <v>446</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>40</v>
@@ -10767,7 +10777,7 @@
         <v>695</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>48</v>
@@ -11797,7 +11807,7 @@
         <v>778</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>83</v>
@@ -12037,7 +12047,7 @@
         <v>807</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>40</v>
@@ -12046,7 +12056,7 @@
         <v>41</v>
       </c>
       <c r="J201" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="K201" s="2" t="s">
         <v>817</v>
@@ -12742,7 +12752,7 @@
         <v>882</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>26</v>
@@ -13204,7 +13214,7 @@
         <v>919</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>48</v>
@@ -13546,7 +13556,7 @@
         <v>939</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>77</v>
+        <v>1207</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>946</v>
@@ -13567,7 +13577,7 @@
         <v>52</v>
       </c>
       <c r="T239" s="3">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="U239" s="3">
         <v>152</v>
@@ -13587,7 +13597,7 @@
         <v>950</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>951</v>
@@ -13619,8 +13629,8 @@
         <v>939</v>
       </c>
       <c r="C241" s="7"/>
-      <c r="D241" s="7" t="s">
-        <v>754</v>
+      <c r="D241" s="7">
+        <v>1637</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>946</v>
@@ -13632,11 +13642,11 @@
       <c r="H241" s="7"/>
       <c r="I241" s="7"/>
       <c r="J241" s="7" t="s">
-        <v>953</v>
+        <v>1206</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="8" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="M241" s="7"/>
       <c r="N241" s="7"/>
@@ -13674,13 +13684,13 @@
         <v>906</v>
       </c>
       <c r="F242" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="J242" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="J242" s="2" t="s">
+      <c r="L242" s="6" t="s">
         <v>956</v>
-      </c>
-      <c r="L242" s="6" t="s">
-        <v>957</v>
       </c>
       <c r="R242" s="2" t="s">
         <v>30</v>
@@ -13715,10 +13725,10 @@
         <v>231</v>
       </c>
       <c r="J243" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="L243" s="6" t="s">
         <v>958</v>
-      </c>
-      <c r="L243" s="6" t="s">
-        <v>959</v>
       </c>
       <c r="R243" s="2" t="s">
         <v>30</v>
@@ -13741,7 +13751,7 @@
         <v>595</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>95</v>
@@ -13753,10 +13763,10 @@
         <v>697</v>
       </c>
       <c r="J244" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="L244" s="6" t="s">
         <v>961</v>
-      </c>
-      <c r="L244" s="6" t="s">
-        <v>962</v>
       </c>
       <c r="R244" s="2" t="s">
         <v>30</v>
@@ -13779,7 +13789,7 @@
         <v>595</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>179</v>
@@ -13788,13 +13798,13 @@
         <v>33</v>
       </c>
       <c r="F245" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="J245" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="J245" s="2" t="s">
+      <c r="L245" s="6" t="s">
         <v>964</v>
-      </c>
-      <c r="L245" s="6" t="s">
-        <v>965</v>
       </c>
       <c r="R245" s="2" t="s">
         <v>30</v>
@@ -13817,7 +13827,7 @@
         <v>595</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>924</v>
@@ -13829,10 +13839,10 @@
         <v>620</v>
       </c>
       <c r="J246" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="L246" s="6" t="s">
         <v>966</v>
-      </c>
-      <c r="L246" s="6" t="s">
-        <v>967</v>
       </c>
       <c r="R246" s="2" t="s">
         <v>30</v>
@@ -13855,7 +13865,7 @@
         <v>595</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>525</v>
@@ -13867,10 +13877,10 @@
         <v>27</v>
       </c>
       <c r="J247" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="L247" s="6" t="s">
         <v>968</v>
-      </c>
-      <c r="L247" s="6" t="s">
-        <v>969</v>
       </c>
       <c r="R247" s="2" t="s">
         <v>30</v>
@@ -13890,10 +13900,10 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>47</v>
@@ -13905,10 +13915,10 @@
         <v>41</v>
       </c>
       <c r="J248" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="L248" s="6" t="s">
         <v>972</v>
-      </c>
-      <c r="L248" s="6" t="s">
-        <v>973</v>
       </c>
       <c r="R248" s="2" t="s">
         <v>30</v>
@@ -13928,25 +13938,25 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B249" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>427</v>
       </c>
       <c r="E249" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="F249" s="2" t="s">
+      <c r="J249" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="J249" s="2" t="s">
+      <c r="L249" s="6" t="s">
         <v>976</v>
-      </c>
-      <c r="L249" s="6" t="s">
-        <v>977</v>
       </c>
       <c r="R249" s="2" t="s">
         <v>30</v>
@@ -13966,10 +13976,10 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="D250" s="2">
         <v>1624</v>
@@ -13981,10 +13991,10 @@
         <v>84</v>
       </c>
       <c r="J250" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="L250" s="6" t="s">
         <v>978</v>
-      </c>
-      <c r="L250" s="6" t="s">
-        <v>979</v>
       </c>
       <c r="R250" s="2" t="s">
         <v>30</v>
@@ -14004,25 +14014,25 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>971</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E251" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="F251" s="2" t="s">
+      <c r="J251" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="J251" s="2" t="s">
+      <c r="L251" s="6" t="s">
         <v>982</v>
-      </c>
-      <c r="L251" s="6" t="s">
-        <v>983</v>
       </c>
       <c r="R251" s="2" t="s">
         <v>30</v>
@@ -14045,7 +14055,7 @@
         <v>88</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D252" s="2">
         <v>1650</v>
@@ -14057,10 +14067,10 @@
         <v>27</v>
       </c>
       <c r="J252" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="L252" s="6" t="s">
         <v>985</v>
-      </c>
-      <c r="L252" s="6" t="s">
-        <v>986</v>
       </c>
       <c r="R252" s="2" t="s">
         <v>30</v>
@@ -14083,7 +14093,7 @@
         <v>88</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>241</v>
@@ -14095,10 +14105,10 @@
         <v>92</v>
       </c>
       <c r="J253" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="L253" s="6" t="s">
         <v>987</v>
-      </c>
-      <c r="L253" s="6" t="s">
-        <v>988</v>
       </c>
       <c r="R253" s="2" t="s">
         <v>30</v>
@@ -14121,7 +14131,7 @@
         <v>88</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D254" s="2">
         <v>1672</v>
@@ -14133,10 +14143,10 @@
         <v>27</v>
       </c>
       <c r="J254" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="L254" s="6" t="s">
         <v>989</v>
-      </c>
-      <c r="L254" s="6" t="s">
-        <v>990</v>
       </c>
       <c r="R254" s="2" t="s">
         <v>30</v>
@@ -14159,7 +14169,7 @@
         <v>88</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D255" s="2">
         <v>1661</v>
@@ -14171,10 +14181,10 @@
         <v>41</v>
       </c>
       <c r="J255" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="L255" s="6" t="s">
         <v>991</v>
-      </c>
-      <c r="L255" s="6" t="s">
-        <v>992</v>
       </c>
       <c r="R255" s="2" t="s">
         <v>30</v>
@@ -14194,10 +14204,10 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>950</v>
@@ -14209,13 +14219,13 @@
         <v>34</v>
       </c>
       <c r="J256" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="K256" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="K256" s="2" t="s">
+      <c r="L256" s="6" t="s">
         <v>996</v>
-      </c>
-      <c r="L256" s="6" t="s">
-        <v>997</v>
       </c>
       <c r="R256" s="2" t="s">
         <v>30</v>
@@ -14235,10 +14245,10 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>950</v>
@@ -14250,10 +14260,10 @@
         <v>84</v>
       </c>
       <c r="J257" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="L257" s="6" t="s">
         <v>998</v>
-      </c>
-      <c r="L257" s="6" t="s">
-        <v>999</v>
       </c>
       <c r="R257" s="2" t="s">
         <v>30</v>
@@ -14273,13 +14283,13 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D258" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>761</v>
@@ -14288,10 +14298,10 @@
         <v>762</v>
       </c>
       <c r="J258" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="L258" s="6" t="s">
         <v>1001</v>
-      </c>
-      <c r="L258" s="6" t="s">
-        <v>1002</v>
       </c>
       <c r="R258" s="2" t="s">
         <v>30</v>
@@ -14311,10 +14321,10 @@
     </row>
     <row r="259" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>257</v>
@@ -14326,13 +14336,13 @@
         <v>27</v>
       </c>
       <c r="J259" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K259" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="K259" s="2" t="s">
+      <c r="L259" s="6" t="s">
         <v>1004</v>
-      </c>
-      <c r="L259" s="6" t="s">
-        <v>1005</v>
       </c>
       <c r="R259" s="2" t="s">
         <v>30</v>
@@ -14352,25 +14362,25 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D260" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F260" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J260" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="J260" s="2" t="s">
+      <c r="L260" s="6" t="s">
         <v>1008</v>
-      </c>
-      <c r="L260" s="6" t="s">
-        <v>1009</v>
       </c>
       <c r="R260" s="2" t="s">
         <v>30</v>
@@ -14390,13 +14400,13 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D261" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>26</v>
@@ -14405,10 +14415,10 @@
         <v>27</v>
       </c>
       <c r="J261" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L261" s="6" t="s">
         <v>1010</v>
-      </c>
-      <c r="L261" s="6" t="s">
-        <v>1011</v>
       </c>
       <c r="R261" s="2" t="s">
         <v>30</v>
@@ -14428,10 +14438,10 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>682</v>
@@ -14443,13 +14453,13 @@
         <v>27</v>
       </c>
       <c r="J262" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K262" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="K262" s="2" t="s">
+      <c r="L262" s="6" t="s">
         <v>1013</v>
-      </c>
-      <c r="L262" s="6" t="s">
-        <v>1014</v>
       </c>
       <c r="R262" s="2" t="s">
         <v>30</v>
@@ -14469,10 +14479,10 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B263" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D263" s="2">
         <v>1668</v>
@@ -14484,13 +14494,13 @@
         <v>762</v>
       </c>
       <c r="J263" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K263" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="K263" s="2" t="s">
+      <c r="L263" s="6" t="s">
         <v>1016</v>
-      </c>
-      <c r="L263" s="6" t="s">
-        <v>1017</v>
       </c>
       <c r="R263" s="2" t="s">
         <v>30</v>
@@ -14510,10 +14520,10 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>343</v>
@@ -14525,13 +14535,13 @@
         <v>84</v>
       </c>
       <c r="J264" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K264" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="K264" s="2" t="s">
+      <c r="L264" s="6" t="s">
         <v>1019</v>
-      </c>
-      <c r="L264" s="6" t="s">
-        <v>1020</v>
       </c>
       <c r="R264" s="2" t="s">
         <v>30</v>
@@ -14551,10 +14561,10 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>491</v>
@@ -14566,13 +14576,13 @@
         <v>97</v>
       </c>
       <c r="J265" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K265" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="K265" s="2" t="s">
+      <c r="L265" s="6" t="s">
         <v>1022</v>
-      </c>
-      <c r="L265" s="6" t="s">
-        <v>1023</v>
       </c>
       <c r="R265" s="2" t="s">
         <v>30</v>
@@ -14592,28 +14602,28 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>994</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>312</v>
       </c>
       <c r="E266" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="F266" s="2" t="s">
+      <c r="J266" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="J266" s="2" t="s">
+      <c r="K266" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="K266" s="2" t="s">
+      <c r="L266" s="6" t="s">
         <v>1027</v>
-      </c>
-      <c r="L266" s="6" t="s">
-        <v>1028</v>
       </c>
       <c r="R266" s="2" t="s">
         <v>30</v>
@@ -14633,28 +14643,28 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>994</v>
-      </c>
       <c r="D267" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J267" s="2" t="s">
         <v>1029</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="J267" s="2" t="s">
-        <v>1030</v>
       </c>
       <c r="K267" s="2" t="s">
         <v>581</v>
       </c>
       <c r="L267" s="6" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="R267" s="2" t="s">
         <v>30</v>
@@ -14677,7 +14687,7 @@
         <v>464</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D268" s="2">
         <v>1653</v>
@@ -14689,10 +14699,10 @@
         <v>92</v>
       </c>
       <c r="J268" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L268" s="6" t="s">
         <v>1033</v>
-      </c>
-      <c r="L268" s="6" t="s">
-        <v>1034</v>
       </c>
       <c r="R268" s="2" t="s">
         <v>30</v>
@@ -14715,7 +14725,7 @@
         <v>464</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>447</v>
@@ -14727,10 +14737,10 @@
         <v>27</v>
       </c>
       <c r="J269" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L269" s="6" t="s">
         <v>1035</v>
-      </c>
-      <c r="L269" s="6" t="s">
-        <v>1036</v>
       </c>
       <c r="R269" s="2" t="s">
         <v>30</v>
@@ -14753,7 +14763,7 @@
         <v>464</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>704</v>
@@ -14765,10 +14775,10 @@
         <v>34</v>
       </c>
       <c r="J270" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L270" s="6" t="s">
         <v>1037</v>
-      </c>
-      <c r="L270" s="6" t="s">
-        <v>1038</v>
       </c>
       <c r="R270" s="2" t="s">
         <v>30</v>
@@ -14791,22 +14801,22 @@
         <v>464</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D271" s="2">
         <v>1660</v>
       </c>
       <c r="E271" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="F271" s="2" t="s">
+      <c r="J271" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="J271" s="2" t="s">
-        <v>1205</v>
-      </c>
       <c r="L271" s="6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="R271" s="2" t="s">
         <v>30</v>
@@ -14829,10 +14839,10 @@
         <v>464</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>40</v>
@@ -14841,13 +14851,13 @@
         <v>41</v>
       </c>
       <c r="J272" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K272" t="s">
         <v>1041</v>
       </c>
-      <c r="K272" t="s">
+      <c r="L272" s="17" t="s">
         <v>1042</v>
-      </c>
-      <c r="L272" s="17" t="s">
-        <v>1043</v>
       </c>
       <c r="R272" s="2" t="s">
         <v>30</v>
@@ -14870,10 +14880,10 @@
         <v>464</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>26</v>
@@ -14882,13 +14892,13 @@
         <v>27</v>
       </c>
       <c r="J273" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="K273" t="s">
         <v>1045</v>
       </c>
-      <c r="K273" t="s">
+      <c r="L273" s="17" t="s">
         <v>1046</v>
-      </c>
-      <c r="L273" s="17" t="s">
-        <v>1047</v>
       </c>
       <c r="R273" s="2" t="s">
         <v>30</v>
@@ -14908,10 +14918,10 @@
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>229</v>
@@ -14923,10 +14933,10 @@
         <v>27</v>
       </c>
       <c r="J274" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L274" s="6" t="s">
         <v>1050</v>
-      </c>
-      <c r="L274" s="6" t="s">
-        <v>1051</v>
       </c>
       <c r="R274" s="2" t="s">
         <v>30</v>
@@ -14946,10 +14956,10 @@
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>179</v>
@@ -14961,10 +14971,10 @@
         <v>84</v>
       </c>
       <c r="J275" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L275" s="6" t="s">
         <v>1052</v>
-      </c>
-      <c r="L275" s="6" t="s">
-        <v>1053</v>
       </c>
       <c r="R275" s="2" t="s">
         <v>30</v>
@@ -14984,10 +14994,10 @@
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B276" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>924</v>
@@ -14999,10 +15009,10 @@
         <v>34</v>
       </c>
       <c r="J276" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L276" s="6" t="s">
         <v>1054</v>
-      </c>
-      <c r="L276" s="6" t="s">
-        <v>1055</v>
       </c>
       <c r="R276" s="2" t="s">
         <v>30</v>
@@ -15022,25 +15032,25 @@
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>1048</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>1049</v>
       </c>
       <c r="D277" s="2">
         <v>1644</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="J277" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L277" s="6" t="s">
         <v>1056</v>
-      </c>
-      <c r="L277" s="6" t="s">
-        <v>1057</v>
       </c>
       <c r="R277" s="2" t="s">
         <v>30</v>
@@ -15060,10 +15070,10 @@
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>754</v>
@@ -15075,13 +15085,13 @@
         <v>49</v>
       </c>
       <c r="J278" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="K278" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="K278" s="2" t="s">
+      <c r="L278" s="6" t="s">
         <v>1061</v>
-      </c>
-      <c r="L278" s="6" t="s">
-        <v>1062</v>
       </c>
       <c r="R278" s="2" t="s">
         <v>30</v>
@@ -15101,13 +15111,13 @@
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>1059</v>
-      </c>
       <c r="D279" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>40</v>
@@ -15116,13 +15126,13 @@
         <v>41</v>
       </c>
       <c r="J279" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K279" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="K279" s="2" t="s">
+      <c r="L279" s="6" t="s">
         <v>1065</v>
-      </c>
-      <c r="L279" s="6" t="s">
-        <v>1066</v>
       </c>
       <c r="R279" s="2" t="s">
         <v>30</v>
@@ -15142,10 +15152,10 @@
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>179</v>
@@ -15154,16 +15164,16 @@
         <v>53</v>
       </c>
       <c r="F280" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="J280" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="J280" s="2" t="s">
+      <c r="K280" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="K280" s="2" t="s">
+      <c r="L280" s="6" t="s">
         <v>1069</v>
-      </c>
-      <c r="L280" s="6" t="s">
-        <v>1070</v>
       </c>
       <c r="R280" s="2" t="s">
         <v>30</v>
@@ -15183,10 +15193,10 @@
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>624</v>
@@ -15198,13 +15208,13 @@
         <v>49</v>
       </c>
       <c r="J281" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K281" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="K281" s="2" t="s">
+      <c r="L281" s="6" t="s">
         <v>1072</v>
-      </c>
-      <c r="L281" s="6" t="s">
-        <v>1073</v>
       </c>
       <c r="R281" s="2" t="s">
         <v>30</v>
@@ -15224,13 +15234,13 @@
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>1059</v>
-      </c>
       <c r="D282" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>40</v>
@@ -15239,13 +15249,13 @@
         <v>41</v>
       </c>
       <c r="J282" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="K282" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="K282" s="2" t="s">
+      <c r="L282" s="6" t="s">
         <v>1076</v>
-      </c>
-      <c r="L282" s="6" t="s">
-        <v>1077</v>
       </c>
       <c r="R282" s="2" t="s">
         <v>30</v>
@@ -15265,13 +15275,13 @@
     </row>
     <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>1059</v>
-      </c>
       <c r="D283" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>48</v>
@@ -15280,13 +15290,13 @@
         <v>49</v>
       </c>
       <c r="J283" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="K283" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="K283" s="2" t="s">
+      <c r="L283" s="6" t="s">
         <v>1080</v>
-      </c>
-      <c r="L283" s="6" t="s">
-        <v>1081</v>
       </c>
       <c r="R283" s="2" t="s">
         <v>30</v>
@@ -15306,28 +15316,28 @@
     </row>
     <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>156</v>
       </c>
       <c r="E284" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>1198</v>
       </c>
-      <c r="F284" s="2" t="s">
-        <v>1199</v>
-      </c>
       <c r="J284" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K284" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="K284" s="2" t="s">
+      <c r="L284" s="6" t="s">
         <v>1083</v>
-      </c>
-      <c r="L284" s="6" t="s">
-        <v>1084</v>
       </c>
       <c r="R284" s="2" t="s">
         <v>30</v>
@@ -15347,10 +15357,10 @@
     </row>
     <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>166</v>
@@ -15362,13 +15372,13 @@
         <v>49</v>
       </c>
       <c r="J285" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="K285" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="K285" s="2" t="s">
-        <v>1086</v>
-      </c>
       <c r="L285" s="17" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="R285" s="2" t="s">
         <v>30</v>
@@ -15388,10 +15398,10 @@
     </row>
     <row r="286" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>359</v>
@@ -15400,16 +15410,16 @@
         <v>96</v>
       </c>
       <c r="F286" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J286" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="J286" s="2" t="s">
+      <c r="K286" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="K286" s="2" t="s">
+      <c r="L286" s="6" t="s">
         <v>1089</v>
-      </c>
-      <c r="L286" s="6" t="s">
-        <v>1090</v>
       </c>
       <c r="R286" s="2" t="s">
         <v>30</v>
@@ -15429,10 +15439,10 @@
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>179</v>
@@ -15444,13 +15454,13 @@
         <v>97</v>
       </c>
       <c r="J287" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="K287" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="K287" s="2" t="s">
+      <c r="L287" s="6" t="s">
         <v>1092</v>
-      </c>
-      <c r="L287" s="6" t="s">
-        <v>1093</v>
       </c>
       <c r="R287" s="2" t="s">
         <v>30</v>
@@ -15470,10 +15480,10 @@
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>188</v>
@@ -15485,13 +15495,13 @@
         <v>49</v>
       </c>
       <c r="J288" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K288" s="2" t="s">
         <v>1094</v>
       </c>
-      <c r="K288" s="2" t="s">
+      <c r="L288" s="6" t="s">
         <v>1095</v>
-      </c>
-      <c r="L288" s="6" t="s">
-        <v>1096</v>
       </c>
       <c r="R288" s="2" t="s">
         <v>30</v>
@@ -15511,13 +15521,13 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>1059</v>
-      </c>
       <c r="D289" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>148</v>
@@ -15526,13 +15536,13 @@
         <v>149</v>
       </c>
       <c r="J289" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K289" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="K289" s="2" t="s">
+      <c r="L289" s="6" t="s">
         <v>1098</v>
-      </c>
-      <c r="L289" s="6" t="s">
-        <v>1099</v>
       </c>
       <c r="R289" s="2" t="s">
         <v>30</v>
@@ -15552,10 +15562,10 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="D290" s="2">
         <v>1660</v>
@@ -15567,13 +15577,13 @@
         <v>27</v>
       </c>
       <c r="J290" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K290" s="2" t="s">
         <v>1102</v>
       </c>
-      <c r="K290" s="2" t="s">
+      <c r="L290" s="6" t="s">
         <v>1103</v>
-      </c>
-      <c r="L290" s="6" t="s">
-        <v>1104</v>
       </c>
       <c r="R290" s="2" t="s">
         <v>30</v>
@@ -15593,10 +15603,10 @@
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>510</v>
@@ -15614,7 +15624,7 @@
         <v>341</v>
       </c>
       <c r="L291" s="6" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="R291" s="2" t="s">
         <v>30</v>
@@ -15634,10 +15644,10 @@
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>1100</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>1101</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>324</v>
@@ -15649,13 +15659,13 @@
         <v>34</v>
       </c>
       <c r="J292" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K292" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="K292" s="2" t="s">
+      <c r="L292" s="6" t="s">
         <v>1107</v>
-      </c>
-      <c r="L292" s="6" t="s">
-        <v>1108</v>
       </c>
       <c r="R292" s="2" t="s">
         <v>30</v>
@@ -15675,13 +15685,13 @@
     </row>
     <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D293" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>148</v>
@@ -15690,13 +15700,13 @@
         <v>149</v>
       </c>
       <c r="J293" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K293" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="K293" s="2" t="s">
+      <c r="L293" s="6" t="s">
         <v>1111</v>
-      </c>
-      <c r="L293" s="6" t="s">
-        <v>1112</v>
       </c>
       <c r="R293" s="2" t="s">
         <v>30</v>
@@ -15716,13 +15726,13 @@
     </row>
     <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D294" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>83</v>
@@ -15731,13 +15741,13 @@
         <v>84</v>
       </c>
       <c r="J294" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K294" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="K294" s="2" t="s">
+      <c r="L294" s="6" t="s">
         <v>1115</v>
-      </c>
-      <c r="L294" s="6" t="s">
-        <v>1116</v>
       </c>
       <c r="R294" s="2" t="s">
         <v>30</v>
@@ -15757,13 +15767,13 @@
     </row>
     <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D295" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>83</v>
@@ -15772,13 +15782,13 @@
         <v>84</v>
       </c>
       <c r="J295" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K295" s="2" t="s">
         <v>1118</v>
       </c>
-      <c r="K295" s="2" t="s">
+      <c r="L295" s="6" t="s">
         <v>1119</v>
-      </c>
-      <c r="L295" s="6" t="s">
-        <v>1120</v>
       </c>
       <c r="R295" s="2" t="s">
         <v>30</v>
@@ -15798,13 +15808,13 @@
     </row>
     <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D296" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>101</v>
@@ -15813,13 +15823,13 @@
         <v>102</v>
       </c>
       <c r="J296" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K296" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="K296" s="2" t="s">
+      <c r="L296" s="6" t="s">
         <v>1123</v>
-      </c>
-      <c r="L296" s="6" t="s">
-        <v>1124</v>
       </c>
       <c r="R296" s="2" t="s">
         <v>30</v>
@@ -15839,13 +15849,13 @@
     </row>
     <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B297" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D297" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>91</v>
@@ -15854,13 +15864,13 @@
         <v>748</v>
       </c>
       <c r="J297" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K297" s="2" t="s">
         <v>1126</v>
       </c>
-      <c r="K297" s="2" t="s">
+      <c r="L297" s="6" t="s">
         <v>1127</v>
-      </c>
-      <c r="L297" s="6" t="s">
-        <v>1128</v>
       </c>
       <c r="R297" s="2" t="s">
         <v>30</v>
@@ -15880,13 +15890,13 @@
     </row>
     <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D298" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>26</v>
@@ -15895,13 +15905,13 @@
         <v>27</v>
       </c>
       <c r="J298" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K298" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="K298" s="2" t="s">
+      <c r="L298" s="6" t="s">
         <v>1131</v>
-      </c>
-      <c r="L298" s="6" t="s">
-        <v>1132</v>
       </c>
       <c r="R298" s="2" t="s">
         <v>30</v>
@@ -15921,13 +15931,13 @@
     </row>
     <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D299" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>688</v>
@@ -15936,13 +15946,13 @@
         <v>689</v>
       </c>
       <c r="J299" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K299" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="K299" s="2" t="s">
+      <c r="L299" s="6" t="s">
         <v>1135</v>
-      </c>
-      <c r="L299" s="6" t="s">
-        <v>1136</v>
       </c>
       <c r="R299" s="2" t="s">
         <v>30</v>
@@ -15962,13 +15972,13 @@
     </row>
     <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D300" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>245</v>
@@ -15977,13 +15987,13 @@
         <v>92</v>
       </c>
       <c r="J300" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K300" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="K300" s="2" t="s">
+      <c r="L300" s="6" t="s">
         <v>1139</v>
-      </c>
-      <c r="L300" s="6" t="s">
-        <v>1140</v>
       </c>
       <c r="R300" s="2" t="s">
         <v>30</v>
@@ -16003,13 +16013,13 @@
     </row>
     <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>1100</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>1101</v>
-      </c>
       <c r="D301" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>230</v>
@@ -16018,13 +16028,13 @@
         <v>231</v>
       </c>
       <c r="J301" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="K301" s="2" t="s">
         <v>1141</v>
       </c>
-      <c r="K301" s="2" t="s">
+      <c r="L301" s="6" t="s">
         <v>1142</v>
-      </c>
-      <c r="L301" s="6" t="s">
-        <v>1143</v>
       </c>
       <c r="R301" s="2" t="s">
         <v>30</v>
@@ -16044,10 +16054,10 @@
     </row>
     <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>1145</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>161</v>
@@ -16059,10 +16069,10 @@
         <v>49</v>
       </c>
       <c r="J302" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L302" s="6" t="s">
         <v>1146</v>
-      </c>
-      <c r="L302" s="6" t="s">
-        <v>1147</v>
       </c>
       <c r="R302" s="2" t="s">
         <v>30</v>
@@ -16082,13 +16092,13 @@
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>1145</v>
-      </c>
       <c r="D303" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>245</v>
@@ -16097,10 +16107,10 @@
         <v>92</v>
       </c>
       <c r="J303" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L303" s="6" t="s">
         <v>1148</v>
-      </c>
-      <c r="L303" s="6" t="s">
-        <v>1149</v>
       </c>
       <c r="R303" s="2" t="s">
         <v>30</v>
@@ -16120,10 +16130,10 @@
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>1145</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>90</v>
@@ -16135,10 +16145,10 @@
         <v>84</v>
       </c>
       <c r="J304" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L304" s="6" t="s">
         <v>1150</v>
-      </c>
-      <c r="L304" s="6" t="s">
-        <v>1151</v>
       </c>
       <c r="R304" s="2" t="s">
         <v>30</v>
@@ -16158,10 +16168,10 @@
     </row>
     <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>1145</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>525</v>
@@ -16173,10 +16183,10 @@
         <v>84</v>
       </c>
       <c r="J305" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L305" s="6" t="s">
         <v>1152</v>
-      </c>
-      <c r="L305" s="6" t="s">
-        <v>1153</v>
       </c>
       <c r="R305" s="2" t="s">
         <v>30</v>
@@ -16196,13 +16206,13 @@
     </row>
     <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B306" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="D306" s="2" t="s">
         <v>1155</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>1156</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>53</v>
@@ -16211,10 +16221,10 @@
         <v>198</v>
       </c>
       <c r="J306" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L306" s="6" t="s">
         <v>1157</v>
-      </c>
-      <c r="L306" s="6" t="s">
-        <v>1158</v>
       </c>
       <c r="R306" s="2" t="s">
         <v>30</v>
@@ -16234,13 +16244,13 @@
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B307" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="B307" s="2" t="s">
-        <v>1155</v>
-      </c>
       <c r="D307" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>53</v>
@@ -16249,10 +16259,10 @@
         <v>334</v>
       </c>
       <c r="J307" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="L307" s="6" t="s">
         <v>1160</v>
-      </c>
-      <c r="L307" s="6" t="s">
-        <v>1161</v>
       </c>
       <c r="R307" s="2" t="s">
         <v>30</v>
@@ -16272,13 +16282,13 @@
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B308" s="2" t="s">
         <v>1154</v>
       </c>
-      <c r="B308" s="2" t="s">
-        <v>1155</v>
-      </c>
       <c r="D308" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>53</v>
@@ -16287,10 +16297,10 @@
         <v>334</v>
       </c>
       <c r="J308" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L308" s="6" t="s">
         <v>1162</v>
-      </c>
-      <c r="L308" s="6" t="s">
-        <v>1163</v>
       </c>
       <c r="R308" s="2" t="s">
         <v>30</v>
@@ -16310,10 +16320,10 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>1154</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>1155</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>466</v>
@@ -16325,10 +16335,10 @@
         <v>781</v>
       </c>
       <c r="J309" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L309" s="6" t="s">
         <v>1164</v>
-      </c>
-      <c r="L309" s="6" t="s">
-        <v>1165</v>
       </c>
       <c r="R309" s="2" t="s">
         <v>30</v>

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -4081,7 +4081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W309"/>
+  <dimension ref="A1:X309"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.85546875" style="2" customWidth="1"/>
@@ -4091,6 +4091,7 @@
     <col min="9" max="9" width="6.7109375" style="2" customWidth="1"/>
     <col min="10" max="19" width="11.85546875" style="2" customWidth="1"/>
     <col min="20" max="23" width="11.85546875" style="3" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4162,6 +4163,11 @@
       </c>
       <c r="W1" s="15" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -4898,13 +4898,13 @@
         <v>30</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="T20" s="3">
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="U20" s="3">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="W20" s="3">
         <v>3</v>
